--- a/app/config/tables/MADTRIAL_FU_PHONE/Forms/MADTRIAL_FU_PHONE/MADTRIAL_FU_PHONE.xlsx
+++ b/app/config/tables/MADTRIAL_FU_PHONE/Forms/MADTRIAL_FU_PHONE/MADTRIAL_FU_PHONE.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="437">
   <si>
     <t>setting_name</t>
   </si>
@@ -448,7 +448,7 @@
     <t>Informador</t>
   </si>
   <si>
-    <t>sim/não/nãosabe</t>
+    <t>sim/nao/naosabe</t>
   </si>
   <si>
     <t>VITALCRI</t>
@@ -539,9 +539,6 @@
   </si>
   <si>
     <t xml:space="preserve">select_one </t>
-  </si>
-  <si>
-    <t>sim/nao/naosabe</t>
   </si>
   <si>
     <t>DIARREIA</t>
@@ -822,6 +819,55 @@
 })</t>
   </si>
   <si>
+    <t>interval_csv</t>
+  </si>
+  <si>
+    <t>"DIAS.csv"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_.chain(context)
+.uniq(function(x) {
+return x.INTERVAL
+})
+.map(function(place){
+return {
+data_value:place.INTERVAL,
+display:{title: {text: place.INTERVAL} } };
+}).value()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_.map(context, function(place){place.data_value = place.DAYS_VALUE;
+place.display = {title: {text: place.DAYS_NAME} };
+return place;
+})</t>
+  </si>
+  <si>
+    <t>bairro_csv</t>
+  </si>
+  <si>
+    <t>"TABZ.csv"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_.chain(context)
+.uniq(function(x) {
+return x.BAIRRONR
+})
+.map(function(place){
+return {
+data_value:place.BAIRRONR,
+display:{title: {text: place.BAIRRO} } };
+}).value()</t>
+  </si>
+  <si>
+    <t>tabz_csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_.map(context, function(place){place.data_value = place.TABZ;
+place.display = {title: {text: place.ZONE} };
+return place;
+})</t>
+  </si>
+  <si>
     <t>choice_list_name</t>
   </si>
   <si>
@@ -939,9 +985,6 @@
     <t>Outro</t>
   </si>
   <si>
-    <t>sim/não</t>
-  </si>
-  <si>
     <t>Eduardo</t>
   </si>
   <si>
@@ -1036,6 +1079,60 @@
   </si>
   <si>
     <t>Bolama</t>
+  </si>
+  <si>
+    <t>Paracetamol</t>
+  </si>
+  <si>
+    <t>Amoxicillina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complexo B</t>
+  </si>
+  <si>
+    <t>Salbutamol</t>
+  </si>
+  <si>
+    <t>Diazepam</t>
+  </si>
+  <si>
+    <t>Prometazina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soro fisiologico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitamina C</t>
+  </si>
+  <si>
+    <t>SRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sulfate de Zinco</t>
+  </si>
+  <si>
+    <t>Azitomicina</t>
+  </si>
+  <si>
+    <t>Brufen</t>
+  </si>
+  <si>
+    <t>Albendazol</t>
+  </si>
+  <si>
+    <t>Mebendazol</t>
+  </si>
+  <si>
+    <t>Metroniazol</t>
+  </si>
+  <si>
+    <t>Nistatina</t>
+  </si>
+  <si>
+    <t>Augmentin</t>
+  </si>
+  <si>
+    <t>Erytromecina</t>
   </si>
   <si>
     <t>calculation_name</t>
@@ -1294,7 +1391,6 @@
     </font>
     <font>
       <sz val="11.000000"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1375,7 +1471,7 @@
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
@@ -1386,9 +1482,8 @@
     <xf fontId="4" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="1"/>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -4701,7 +4796,7 @@
       <c r="D6" t="s">
         <v>61</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="8" t="s">
         <v>139</v>
       </c>
       <c r="F6" t="s">
@@ -4771,7 +4866,7 @@
       <c r="F11" t="s">
         <v>144</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="9" t="s">
         <v>154</v>
       </c>
     </row>
@@ -4841,2056 +4936,2056 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9"/>
-      <c r="B19" s="10" t="s">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
     </row>
     <row r="20">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10" t="s">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10" t="s">
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
     </row>
     <row r="21">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10" t="s">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="G21" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="H21" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10" t="s">
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="I24" s="8"/>
+      <c r="J24" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="K24" s="8"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C30" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10" t="s">
+      <c r="F31" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I31" s="10"/>
+      <c r="J31" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8"/>
+      <c r="B32" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="I38" s="8"/>
+      <c r="J38" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="K38" s="8"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="10"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="10"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="10"/>
+      <c r="P41" s="10"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="10"/>
+      <c r="P42" s="10"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="10"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="10"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="I45" s="8"/>
+      <c r="J45" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="K45" s="8"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8"/>
+      <c r="B47" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="10"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="10"/>
+      <c r="P48" s="10"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="10"/>
+      <c r="P49" s="10"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="I52" s="8"/>
+      <c r="J52" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="K52" s="8"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="10"/>
+      <c r="P52" s="10"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="10"/>
+      <c r="P53" s="10"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10"/>
+      <c r="P54" s="10"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8"/>
+      <c r="B55" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="10"/>
+      <c r="P55" s="10"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I56" s="8"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="10"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="10"/>
+      <c r="P57" s="10"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8"/>
+      <c r="B58" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="10"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="10"/>
+      <c r="P58" s="10"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F24" s="10" t="s">
+      <c r="E59" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="G59" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="H59" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="I59" s="8"/>
+      <c r="J59" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="I24" s="10"/>
-      <c r="J24" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="K24" s="10"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10" t="s">
+      <c r="K59" s="8"/>
+      <c r="L59" s="10"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="10"/>
+      <c r="P59" s="10"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8"/>
+      <c r="B60" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10" t="s">
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="10"/>
+      <c r="H60" s="10"/>
+      <c r="I60" s="10"/>
+      <c r="J60" s="10"/>
+      <c r="K60" s="10"/>
+      <c r="L60" s="10"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="10"/>
+      <c r="P60" s="10"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8"/>
+      <c r="B61" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10" t="s">
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="10"/>
+      <c r="P61" s="10"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="8"/>
+      <c r="B62" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10" t="s">
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="10"/>
+      <c r="I62" s="10"/>
+      <c r="J62" s="10"/>
+      <c r="K62" s="10"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="10"/>
+      <c r="P62" s="10"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10" t="s">
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+      <c r="G63" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H63" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10" t="s">
+      <c r="I63" s="8"/>
+      <c r="J63" s="8"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="10"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="10"/>
+      <c r="P63" s="10"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="11"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10" t="s">
+      <c r="E64" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="I64" s="8"/>
+      <c r="J64" s="8"/>
+      <c r="K64" s="8"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="10"/>
+      <c r="P64" s="10"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10" t="s">
+      <c r="C65" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="8"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="10"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="10"/>
+      <c r="P65" s="10"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E31" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="G31" s="11" t="s">
+      <c r="E66" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="H66" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="H31" s="11" t="s">
+      <c r="I66" s="8"/>
+      <c r="J66" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="I31" s="11"/>
-      <c r="J31" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="11"/>
-      <c r="P31" s="11"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11" t="s">
+      <c r="K66" s="8"/>
+      <c r="L66" s="10"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="10"/>
+      <c r="P66" s="10"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="8"/>
+      <c r="B67" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="11"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10" t="s">
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="8"/>
+      <c r="K67" s="8"/>
+      <c r="L67" s="10"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="10"/>
+      <c r="P67" s="10"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="11"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="11"/>
-      <c r="P34" s="11"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10" t="s">
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="8"/>
+      <c r="J68" s="8"/>
+      <c r="K68" s="8"/>
+      <c r="L68" s="10"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="10"/>
+      <c r="P68" s="10"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="8"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8"/>
+      <c r="J69" s="8"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="10"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="10"/>
+      <c r="P69" s="10"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10" t="s">
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H70" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="11"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10" t="s">
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="10"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="10"/>
+      <c r="P70" s="10"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E36" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="11"/>
-      <c r="P36" s="11"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10" t="s">
+      <c r="E71" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="I71" s="8"/>
+      <c r="J71" s="8"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="10"/>
+      <c r="P71" s="10"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8"/>
+      <c r="B72" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="11"/>
-      <c r="P37" s="11"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="G38" s="10" t="s">
+      <c r="C72" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="10"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="10"/>
+      <c r="O72" s="10"/>
+      <c r="P72" s="10"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="8"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="H73" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="I73" s="8"/>
+      <c r="J73" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="I38" s="10"/>
-      <c r="J38" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="K38" s="10"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="11"/>
-      <c r="P38" s="11"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10" t="s">
+      <c r="K73" s="8"/>
+      <c r="L73" s="10"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="10"/>
+      <c r="P73" s="10"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8"/>
+      <c r="B74" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-      <c r="O39" s="11"/>
-      <c r="P39" s="11"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10" t="s">
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="10"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="10"/>
+      <c r="P74" s="10"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8"/>
+      <c r="B75" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-      <c r="O40" s="11"/>
-      <c r="P40" s="11"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10" t="s">
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="10"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="10"/>
+      <c r="P75" s="10"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="8"/>
+      <c r="B76" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11"/>
-      <c r="P41" s="11"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10" t="s">
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="10"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="10"/>
+      <c r="O76" s="10"/>
+      <c r="P76" s="10"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="8"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10" t="s">
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H77" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="11"/>
-      <c r="O42" s="11"/>
-      <c r="P42" s="11"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="10"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10" t="s">
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="10"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="10"/>
+      <c r="O77" s="10"/>
+      <c r="P77" s="10"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="8"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E43" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="11"/>
-      <c r="P43" s="11"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10"/>
-      <c r="B44" s="10" t="s">
+      <c r="E78" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="10"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="10"/>
+      <c r="O78" s="10"/>
+      <c r="P78" s="10"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="8"/>
+      <c r="B79" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="11"/>
-      <c r="P44" s="11"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="G45" s="10" t="s">
+      <c r="C79" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="10"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="10"/>
+      <c r="O79" s="10"/>
+      <c r="P79" s="10"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="H80" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="I80" s="8"/>
+      <c r="J80" s="8"/>
+      <c r="K80" s="8"/>
+      <c r="L80" s="10"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="10"/>
+      <c r="O80" s="10"/>
+      <c r="P80" s="10"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="H81" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="I81" s="8"/>
+      <c r="J81" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="I45" s="10"/>
-      <c r="J45" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="K45" s="10"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="11"/>
-      <c r="O45" s="11"/>
-      <c r="P45" s="11"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10" t="s">
+      <c r="K81" s="8"/>
+      <c r="L81" s="10"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="10"/>
+      <c r="O81" s="10"/>
+      <c r="P81" s="10"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="8"/>
+      <c r="B82" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="11"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10" t="s">
+      <c r="C82" s="8"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="8"/>
+      <c r="J82" s="8"/>
+      <c r="K82" s="8"/>
+      <c r="L82" s="10"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="10"/>
+      <c r="O82" s="10"/>
+      <c r="P82" s="10"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8"/>
+      <c r="B83" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="11"/>
-      <c r="O47" s="11"/>
-      <c r="P47" s="11"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="10"/>
-      <c r="B48" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="11"/>
-      <c r="O48" s="11"/>
-      <c r="P48" s="11"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="10"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10" t="s">
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="10"/>
+      <c r="M83" s="10"/>
+      <c r="N83" s="10"/>
+      <c r="O83" s="10"/>
+      <c r="P83" s="10"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8"/>
+      <c r="B84" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="10"/>
+      <c r="M84" s="10"/>
+      <c r="N84" s="10"/>
+      <c r="O84" s="10"/>
+      <c r="P84" s="10"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10" t="s">
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H85" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="11"/>
-      <c r="O49" s="11"/>
-      <c r="P49" s="11"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="10"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10" t="s">
+      <c r="I85" s="8"/>
+      <c r="J85" s="8"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="10"/>
+      <c r="M85" s="10"/>
+      <c r="N85" s="10"/>
+      <c r="O85" s="10"/>
+      <c r="P85" s="10"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8"/>
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E50" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
-      <c r="O50" s="11"/>
-      <c r="P50" s="11"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="10"/>
-      <c r="B51" s="10" t="s">
+      <c r="E86" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="I86" s="8"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="10"/>
+      <c r="M86" s="10"/>
+      <c r="N86" s="10"/>
+      <c r="O86" s="10"/>
+      <c r="P86" s="10"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8"/>
+      <c r="B87" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11"/>
-      <c r="O51" s="11"/>
-      <c r="P51" s="11"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="10"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="G52" s="10" t="s">
+      <c r="C87" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="D87" s="8"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="8"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="10"/>
+      <c r="M87" s="10"/>
+      <c r="N87" s="10"/>
+      <c r="O87" s="10"/>
+      <c r="P87" s="10"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="8"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="H88" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="H52" s="10" t="s">
+      <c r="I88" s="8"/>
+      <c r="J88" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="I52" s="10"/>
-      <c r="J52" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="K52" s="10"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="11"/>
-      <c r="O52" s="11"/>
-      <c r="P52" s="11"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="10"/>
-      <c r="B53" s="10" t="s">
+      <c r="K88" s="8"/>
+      <c r="L88" s="10"/>
+      <c r="M88" s="10"/>
+      <c r="N88" s="10"/>
+      <c r="O88" s="10"/>
+      <c r="P88" s="10"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="8"/>
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="E89" s="8"/>
+      <c r="F89" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="I89" s="10"/>
+      <c r="J89" s="10"/>
+      <c r="K89" s="10"/>
+      <c r="L89" s="10"/>
+      <c r="M89" s="10"/>
+      <c r="N89" s="10"/>
+      <c r="O89" s="10"/>
+      <c r="P89" s="10"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="8"/>
+      <c r="B90" s="10"/>
+      <c r="C90" s="10"/>
+      <c r="D90" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H90" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="I90" s="10"/>
+      <c r="J90" s="10"/>
+      <c r="K90" s="10"/>
+      <c r="L90" s="10"/>
+      <c r="M90" s="10"/>
+      <c r="N90" s="10"/>
+      <c r="O90" s="10"/>
+      <c r="P90" s="10"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="8"/>
+      <c r="B91" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="11"/>
-      <c r="O53" s="11"/>
-      <c r="P53" s="11"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="10"/>
-      <c r="B54" s="10" t="s">
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="10"/>
+      <c r="F91" s="10"/>
+      <c r="G91" s="10"/>
+      <c r="H91" s="10"/>
+      <c r="I91" s="10"/>
+      <c r="J91" s="10"/>
+      <c r="K91" s="10"/>
+      <c r="L91" s="10"/>
+      <c r="M91" s="10"/>
+      <c r="N91" s="10"/>
+      <c r="O91" s="10"/>
+      <c r="P91" s="10"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="8"/>
+      <c r="B92" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="11"/>
-      <c r="O54" s="11"/>
-      <c r="P54" s="11"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="10"/>
-      <c r="B55" s="10" t="s">
+      <c r="C92" s="8"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="8"/>
+      <c r="J92" s="8"/>
+      <c r="K92" s="8"/>
+      <c r="L92" s="10"/>
+      <c r="M92" s="10"/>
+      <c r="N92" s="10"/>
+      <c r="O92" s="10"/>
+      <c r="P92" s="10"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="8"/>
+      <c r="B93" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10"/>
-      <c r="L55" s="11"/>
-      <c r="M55" s="11"/>
-      <c r="N55" s="11"/>
-      <c r="O55" s="11"/>
-      <c r="P55" s="11"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="10"/>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10" t="s">
+      <c r="C93" s="8"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="8"/>
+      <c r="J93" s="8"/>
+      <c r="K93" s="8"/>
+      <c r="L93" s="10"/>
+      <c r="M93" s="10"/>
+      <c r="N93" s="10"/>
+      <c r="O93" s="10"/>
+      <c r="P93" s="10"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="8"/>
+      <c r="B94" s="8"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10" t="s">
+      <c r="E94" s="8"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="H56" s="10" t="s">
+      <c r="H94" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="11"/>
-      <c r="O56" s="11"/>
-      <c r="P56" s="11"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="10"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10" t="s">
+      <c r="I94" s="8"/>
+      <c r="J94" s="8"/>
+      <c r="K94" s="8"/>
+      <c r="L94" s="10"/>
+      <c r="M94" s="10"/>
+      <c r="N94" s="10"/>
+      <c r="O94" s="10"/>
+      <c r="P94" s="10"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="8"/>
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E57" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10"/>
-      <c r="L57" s="11"/>
-      <c r="M57" s="11"/>
-      <c r="N57" s="11"/>
-      <c r="O57" s="11"/>
-      <c r="P57" s="11"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10"/>
-      <c r="B58" s="10" t="s">
+      <c r="E95" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="I95" s="8"/>
+      <c r="J95" s="8"/>
+      <c r="K95" s="8"/>
+      <c r="L95" s="10"/>
+      <c r="M95" s="10"/>
+      <c r="N95" s="10"/>
+      <c r="O95" s="10"/>
+      <c r="P95" s="10"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="8"/>
+      <c r="B96" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
-      <c r="K58" s="10"/>
-      <c r="L58" s="11"/>
-      <c r="M58" s="11"/>
-      <c r="N58" s="11"/>
-      <c r="O58" s="11"/>
-      <c r="P58" s="11"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="10"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10" t="s">
+      <c r="C96" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="D96" s="8"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="8"/>
+      <c r="J96" s="8"/>
+      <c r="K96" s="8"/>
+      <c r="L96" s="10"/>
+      <c r="M96" s="10"/>
+      <c r="N96" s="10"/>
+      <c r="O96" s="10"/>
+      <c r="P96" s="10"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="8"/>
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E59" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="G59" s="10" t="s">
+      <c r="E97" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="H97" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="H59" s="10" t="s">
+      <c r="I97" s="8"/>
+      <c r="J97" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="I59" s="10"/>
-      <c r="J59" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="K59" s="10"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="11"/>
-      <c r="O59" s="11"/>
-      <c r="P59" s="11"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="10"/>
-      <c r="B60" s="10" t="s">
+      <c r="K97" s="8"/>
+      <c r="L97" s="10"/>
+      <c r="M97" s="10"/>
+      <c r="N97" s="10"/>
+      <c r="O97" s="10"/>
+      <c r="P97" s="10"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="8"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="12"/>
+      <c r="D98" s="12"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
+      <c r="H98" s="12"/>
+      <c r="I98" s="12"/>
+      <c r="J98" s="12"/>
+      <c r="K98" s="8"/>
+      <c r="L98" s="10"/>
+      <c r="M98" s="10"/>
+      <c r="N98" s="10"/>
+      <c r="O98" s="10"/>
+      <c r="P98" s="10"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="8"/>
+      <c r="B99" s="12"/>
+      <c r="C99" s="12"/>
+      <c r="D99" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="F99" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="G99" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="H99" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="I99" s="12"/>
+      <c r="J99" s="12"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="10"/>
+      <c r="M99" s="10"/>
+      <c r="N99" s="10"/>
+      <c r="O99" s="10"/>
+      <c r="P99" s="10"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="8"/>
+      <c r="B100" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="D100" s="12"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
+      <c r="H100" s="12"/>
+      <c r="I100" s="12"/>
+      <c r="J100" s="12"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="10"/>
+      <c r="M100" s="10"/>
+      <c r="N100" s="10"/>
+      <c r="O100" s="10"/>
+      <c r="P100" s="10"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="8"/>
+      <c r="B101" s="12"/>
+      <c r="C101" s="12"/>
+      <c r="D101" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="E101" s="12"/>
+      <c r="F101" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="G101" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="H101" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="I101" s="12"/>
+      <c r="J101" s="12"/>
+      <c r="K101" s="8"/>
+      <c r="L101" s="10"/>
+      <c r="M101" s="10"/>
+      <c r="N101" s="10"/>
+      <c r="O101" s="10"/>
+      <c r="P101" s="10"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="8"/>
+      <c r="B102" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="11"/>
-      <c r="I60" s="11"/>
-      <c r="J60" s="11"/>
-      <c r="K60" s="11"/>
-      <c r="L60" s="11"/>
-      <c r="M60" s="11"/>
-      <c r="N60" s="11"/>
-      <c r="O60" s="11"/>
-      <c r="P60" s="11"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="10"/>
-      <c r="B61" s="11" t="s">
+      <c r="C102" s="12"/>
+      <c r="D102" s="12"/>
+      <c r="E102" s="12"/>
+      <c r="F102" s="12"/>
+      <c r="G102" s="12"/>
+      <c r="H102" s="12"/>
+      <c r="I102" s="12"/>
+      <c r="J102" s="12"/>
+      <c r="K102" s="8"/>
+      <c r="L102" s="10"/>
+      <c r="M102" s="10"/>
+      <c r="N102" s="10"/>
+      <c r="O102" s="10"/>
+      <c r="P102" s="10"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="8"/>
+      <c r="B103" s="12"/>
+      <c r="C103" s="12"/>
+      <c r="D103" s="12"/>
+      <c r="E103" s="12"/>
+      <c r="F103" s="12"/>
+      <c r="G103" s="12"/>
+      <c r="H103" s="12"/>
+      <c r="I103" s="12"/>
+      <c r="J103" s="12"/>
+      <c r="K103" s="8"/>
+      <c r="L103" s="10"/>
+      <c r="M103" s="10"/>
+      <c r="N103" s="10"/>
+      <c r="O103" s="10"/>
+      <c r="P103" s="10"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="8"/>
+      <c r="B104" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C104" s="8"/>
+      <c r="D104" s="8"/>
+      <c r="E104" s="8"/>
+      <c r="F104" s="8"/>
+      <c r="G104" s="8"/>
+      <c r="H104" s="8"/>
+      <c r="I104" s="8"/>
+      <c r="J104" s="8"/>
+      <c r="K104" s="8"/>
+      <c r="L104" s="10"/>
+      <c r="M104" s="10"/>
+      <c r="N104" s="10"/>
+      <c r="O104" s="10"/>
+      <c r="P104" s="10"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="8"/>
+      <c r="B105" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="11"/>
-      <c r="J61" s="11"/>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
-      <c r="M61" s="11"/>
-      <c r="N61" s="11"/>
-      <c r="O61" s="11"/>
-      <c r="P61" s="11"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="10"/>
-      <c r="B62" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="11"/>
-      <c r="I62" s="11"/>
-      <c r="J62" s="11"/>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
-      <c r="M62" s="11"/>
-      <c r="N62" s="11"/>
-      <c r="O62" s="11"/>
-      <c r="P62" s="11"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="10"/>
-      <c r="B63" s="10"/>
-      <c r="C63" s="10"/>
-      <c r="D63" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E63" s="10"/>
-      <c r="F63" s="10"/>
-      <c r="G63" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="11"/>
-      <c r="O63" s="11"/>
-      <c r="P63" s="11"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="10"/>
-      <c r="B64" s="10"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="G64" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="H64" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="I64" s="10"/>
-      <c r="J64" s="10"/>
-      <c r="K64" s="10"/>
-      <c r="L64" s="11"/>
-      <c r="M64" s="11"/>
-      <c r="N64" s="11"/>
-      <c r="O64" s="11"/>
-      <c r="P64" s="11"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="10"/>
-      <c r="B65" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10"/>
-      <c r="K65" s="10"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="11"/>
-      <c r="O65" s="11"/>
-      <c r="P65" s="11"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="10"/>
-      <c r="B66" s="10"/>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F66" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="G66" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="I66" s="10"/>
-      <c r="J66" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="K66" s="10"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="11"/>
-      <c r="O66" s="11"/>
-      <c r="P66" s="11"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10"/>
-      <c r="B67" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="10"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
-      <c r="K67" s="10"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="11"/>
-      <c r="O67" s="11"/>
-      <c r="P67" s="11"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="10"/>
-      <c r="B68" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="10"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="10"/>
-      <c r="K68" s="10"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="11"/>
-      <c r="O68" s="11"/>
-      <c r="P68" s="11"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="10"/>
-      <c r="B69" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C69" s="10"/>
-      <c r="D69" s="10"/>
-      <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="10"/>
-      <c r="H69" s="10"/>
-      <c r="I69" s="10"/>
-      <c r="J69" s="10"/>
-      <c r="K69" s="10"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="11"/>
-      <c r="O69" s="11"/>
-      <c r="P69" s="11"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="10"/>
-      <c r="B70" s="10"/>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="H70" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="I70" s="10"/>
-      <c r="J70" s="10"/>
-      <c r="K70" s="10"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
-      <c r="N70" s="11"/>
-      <c r="O70" s="11"/>
-      <c r="P70" s="11"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="10"/>
-      <c r="B71" s="10"/>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F71" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
-      <c r="K71" s="10"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="11"/>
-      <c r="O71" s="11"/>
-      <c r="P71" s="11"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="10"/>
-      <c r="B72" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="D72" s="10"/>
-      <c r="E72" s="10"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="10"/>
-      <c r="H72" s="10"/>
-      <c r="I72" s="10"/>
-      <c r="J72" s="10"/>
-      <c r="K72" s="10"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="11"/>
-      <c r="O72" s="11"/>
-      <c r="P72" s="11"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="10"/>
-      <c r="B73" s="10"/>
-      <c r="C73" s="10"/>
-      <c r="D73" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E73" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F73" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="G73" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="I73" s="10"/>
-      <c r="J73" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="K73" s="10"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="11"/>
-      <c r="O73" s="11"/>
-      <c r="P73" s="11"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="10"/>
-      <c r="B74" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C74" s="10"/>
-      <c r="D74" s="10"/>
-      <c r="E74" s="10"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
-      <c r="I74" s="10"/>
-      <c r="J74" s="10"/>
-      <c r="K74" s="10"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="11"/>
-      <c r="N74" s="11"/>
-      <c r="O74" s="11"/>
-      <c r="P74" s="11"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="10"/>
-      <c r="B75" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="10"/>
-      <c r="G75" s="10"/>
-      <c r="H75" s="10"/>
-      <c r="I75" s="10"/>
-      <c r="J75" s="10"/>
-      <c r="K75" s="10"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="11"/>
-      <c r="O75" s="11"/>
-      <c r="P75" s="11"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="10"/>
-      <c r="B76" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="10"/>
-      <c r="I76" s="10"/>
-      <c r="J76" s="10"/>
-      <c r="K76" s="10"/>
-      <c r="L76" s="11"/>
-      <c r="M76" s="11"/>
-      <c r="N76" s="11"/>
-      <c r="O76" s="11"/>
-      <c r="P76" s="11"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="10"/>
-      <c r="B77" s="10"/>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E77" s="10"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="I77" s="10"/>
-      <c r="J77" s="10"/>
-      <c r="K77" s="10"/>
-      <c r="L77" s="11"/>
-      <c r="M77" s="11"/>
-      <c r="N77" s="11"/>
-      <c r="O77" s="11"/>
-      <c r="P77" s="11"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="10"/>
-      <c r="B78" s="10"/>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F78" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="H78" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="I78" s="10"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="10"/>
-      <c r="L78" s="11"/>
-      <c r="M78" s="11"/>
-      <c r="N78" s="11"/>
-      <c r="O78" s="11"/>
-      <c r="P78" s="11"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="10"/>
-      <c r="B79" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C79" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="10"/>
-      <c r="H79" s="10"/>
-      <c r="I79" s="10"/>
-      <c r="J79" s="10"/>
-      <c r="K79" s="10"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
-      <c r="N79" s="11"/>
-      <c r="O79" s="11"/>
-      <c r="P79" s="11"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="10"/>
-      <c r="B80" s="10"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="H80" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="I80" s="10"/>
-      <c r="J80" s="10"/>
-      <c r="K80" s="10"/>
-      <c r="L80" s="11"/>
-      <c r="M80" s="11"/>
-      <c r="N80" s="11"/>
-      <c r="O80" s="11"/>
-      <c r="P80" s="11"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="10"/>
-      <c r="B81" s="10"/>
-      <c r="C81" s="10"/>
-      <c r="D81" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F81" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="G81" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="I81" s="10"/>
-      <c r="J81" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="K81" s="10"/>
-      <c r="L81" s="11"/>
-      <c r="M81" s="11"/>
-      <c r="N81" s="11"/>
-      <c r="O81" s="11"/>
-      <c r="P81" s="11"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="10"/>
-      <c r="B82" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C82" s="10"/>
-      <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="10"/>
-      <c r="H82" s="10"/>
-      <c r="I82" s="10"/>
-      <c r="J82" s="10"/>
-      <c r="K82" s="10"/>
-      <c r="L82" s="11"/>
-      <c r="M82" s="11"/>
-      <c r="N82" s="11"/>
-      <c r="O82" s="11"/>
-      <c r="P82" s="11"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="10"/>
-      <c r="B83" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C83" s="10"/>
-      <c r="D83" s="10"/>
-      <c r="E83" s="10"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="10"/>
-      <c r="H83" s="10"/>
-      <c r="I83" s="10"/>
-      <c r="J83" s="10"/>
-      <c r="K83" s="10"/>
-      <c r="L83" s="11"/>
-      <c r="M83" s="11"/>
-      <c r="N83" s="11"/>
-      <c r="O83" s="11"/>
-      <c r="P83" s="11"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="10"/>
-      <c r="B84" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C84" s="10"/>
-      <c r="D84" s="10"/>
-      <c r="E84" s="10"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="10"/>
-      <c r="H84" s="10"/>
-      <c r="I84" s="10"/>
-      <c r="J84" s="10"/>
-      <c r="K84" s="10"/>
-      <c r="L84" s="11"/>
-      <c r="M84" s="11"/>
-      <c r="N84" s="11"/>
-      <c r="O84" s="11"/>
-      <c r="P84" s="11"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="10"/>
-      <c r="B85" s="10"/>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E85" s="10"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="I85" s="10"/>
-      <c r="J85" s="10"/>
-      <c r="K85" s="10"/>
-      <c r="L85" s="11"/>
-      <c r="M85" s="11"/>
-      <c r="N85" s="11"/>
-      <c r="O85" s="11"/>
-      <c r="P85" s="11"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="10"/>
-      <c r="B86" s="10"/>
-      <c r="C86" s="10"/>
-      <c r="D86" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F86" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="G86" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="H86" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="I86" s="10"/>
-      <c r="J86" s="10"/>
-      <c r="K86" s="10"/>
-      <c r="L86" s="11"/>
-      <c r="M86" s="11"/>
-      <c r="N86" s="11"/>
-      <c r="O86" s="11"/>
-      <c r="P86" s="11"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="10"/>
-      <c r="B87" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="D87" s="10"/>
-      <c r="E87" s="10"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="10"/>
-      <c r="H87" s="10"/>
-      <c r="I87" s="10"/>
-      <c r="J87" s="10"/>
-      <c r="K87" s="10"/>
-      <c r="L87" s="11"/>
-      <c r="M87" s="11"/>
-      <c r="N87" s="11"/>
-      <c r="O87" s="11"/>
-      <c r="P87" s="11"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="10"/>
-      <c r="B88" s="10"/>
-      <c r="C88" s="10"/>
-      <c r="D88" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F88" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="G88" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="H88" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="I88" s="10"/>
-      <c r="J88" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="K88" s="10"/>
-      <c r="L88" s="11"/>
-      <c r="M88" s="11"/>
-      <c r="N88" s="11"/>
-      <c r="O88" s="11"/>
-      <c r="P88" s="11"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="10"/>
-      <c r="B89" s="10"/>
-      <c r="C89" s="10"/>
-      <c r="D89" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="E89" s="10"/>
-      <c r="F89" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="G89" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="H89" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="I89" s="11"/>
-      <c r="J89" s="11"/>
-      <c r="K89" s="11"/>
-      <c r="L89" s="11"/>
-      <c r="M89" s="11"/>
-      <c r="N89" s="11"/>
-      <c r="O89" s="11"/>
-      <c r="P89" s="11"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="10"/>
-      <c r="B90" s="11"/>
-      <c r="C90" s="11"/>
-      <c r="D90" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E90" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="F90" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="G90" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="H90" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="I90" s="11"/>
-      <c r="J90" s="11"/>
-      <c r="K90" s="11"/>
-      <c r="L90" s="11"/>
-      <c r="M90" s="11"/>
-      <c r="N90" s="11"/>
-      <c r="O90" s="11"/>
-      <c r="P90" s="11"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="10"/>
-      <c r="B91" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C91" s="10"/>
-      <c r="D91" s="10"/>
-      <c r="E91" s="11"/>
-      <c r="F91" s="11"/>
-      <c r="G91" s="11"/>
-      <c r="H91" s="11"/>
-      <c r="I91" s="11"/>
-      <c r="J91" s="11"/>
-      <c r="K91" s="11"/>
-      <c r="L91" s="11"/>
-      <c r="M91" s="11"/>
-      <c r="N91" s="11"/>
-      <c r="O91" s="11"/>
-      <c r="P91" s="11"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="10"/>
-      <c r="B92" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C92" s="10"/>
-      <c r="D92" s="10"/>
-      <c r="E92" s="10"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="10"/>
-      <c r="H92" s="10"/>
-      <c r="I92" s="10"/>
-      <c r="J92" s="10"/>
-      <c r="K92" s="10"/>
-      <c r="L92" s="11"/>
-      <c r="M92" s="11"/>
-      <c r="N92" s="11"/>
-      <c r="O92" s="11"/>
-      <c r="P92" s="11"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="10"/>
-      <c r="B93" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C93" s="10"/>
-      <c r="D93" s="10"/>
-      <c r="E93" s="10"/>
-      <c r="F93" s="10"/>
-      <c r="G93" s="10"/>
-      <c r="H93" s="10"/>
-      <c r="I93" s="10"/>
-      <c r="J93" s="10"/>
-      <c r="K93" s="10"/>
-      <c r="L93" s="11"/>
-      <c r="M93" s="11"/>
-      <c r="N93" s="11"/>
-      <c r="O93" s="11"/>
-      <c r="P93" s="11"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="10"/>
-      <c r="B94" s="10"/>
-      <c r="C94" s="10"/>
-      <c r="D94" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="H94" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="I94" s="10"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="11"/>
-      <c r="M94" s="11"/>
-      <c r="N94" s="11"/>
-      <c r="O94" s="11"/>
-      <c r="P94" s="11"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="10"/>
-      <c r="B95" s="10"/>
-      <c r="C95" s="10"/>
-      <c r="D95" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E95" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F95" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="G95" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="I95" s="10"/>
-      <c r="J95" s="10"/>
-      <c r="K95" s="10"/>
-      <c r="L95" s="11"/>
-      <c r="M95" s="11"/>
-      <c r="N95" s="11"/>
-      <c r="O95" s="11"/>
-      <c r="P95" s="11"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="10"/>
-      <c r="B96" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C96" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="D96" s="10"/>
-      <c r="E96" s="10"/>
-      <c r="F96" s="10"/>
-      <c r="G96" s="10"/>
-      <c r="H96" s="10"/>
-      <c r="I96" s="10"/>
-      <c r="J96" s="10"/>
-      <c r="K96" s="10"/>
-      <c r="L96" s="11"/>
-      <c r="M96" s="11"/>
-      <c r="N96" s="11"/>
-      <c r="O96" s="11"/>
-      <c r="P96" s="11"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="10"/>
-      <c r="B97" s="10"/>
-      <c r="C97" s="10"/>
-      <c r="D97" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E97" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F97" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="G97" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="I97" s="10"/>
-      <c r="J97" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="K97" s="10"/>
-      <c r="L97" s="11"/>
-      <c r="M97" s="11"/>
-      <c r="N97" s="11"/>
-      <c r="O97" s="11"/>
-      <c r="P97" s="11"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="10"/>
-      <c r="B98" s="13"/>
-      <c r="C98" s="13"/>
-      <c r="D98" s="13"/>
-      <c r="E98" s="13"/>
-      <c r="F98" s="13"/>
-      <c r="G98" s="13"/>
-      <c r="H98" s="13"/>
-      <c r="I98" s="13"/>
-      <c r="J98" s="13"/>
-      <c r="K98" s="10"/>
-      <c r="L98" s="11"/>
-      <c r="M98" s="11"/>
-      <c r="N98" s="11"/>
-      <c r="O98" s="11"/>
-      <c r="P98" s="11"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="10"/>
-      <c r="B99" s="13"/>
-      <c r="C99" s="13"/>
-      <c r="D99" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E99" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="F99" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="G99" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="H99" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="I99" s="13"/>
-      <c r="J99" s="13"/>
-      <c r="K99" s="10"/>
-      <c r="L99" s="11"/>
-      <c r="M99" s="11"/>
-      <c r="N99" s="11"/>
-      <c r="O99" s="11"/>
-      <c r="P99" s="11"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="10"/>
-      <c r="B100" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C100" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="D100" s="13"/>
-      <c r="E100" s="13"/>
-      <c r="F100" s="13"/>
-      <c r="G100" s="13"/>
-      <c r="H100" s="13"/>
-      <c r="I100" s="13"/>
-      <c r="J100" s="13"/>
-      <c r="K100" s="10"/>
-      <c r="L100" s="11"/>
-      <c r="M100" s="11"/>
-      <c r="N100" s="11"/>
-      <c r="O100" s="11"/>
-      <c r="P100" s="11"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="10"/>
-      <c r="B101" s="13"/>
-      <c r="C101" s="13"/>
-      <c r="D101" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="E101" s="13"/>
-      <c r="F101" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="G101" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="H101" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="I101" s="13"/>
-      <c r="J101" s="13"/>
-      <c r="K101" s="10"/>
-      <c r="L101" s="11"/>
-      <c r="M101" s="11"/>
-      <c r="N101" s="11"/>
-      <c r="O101" s="11"/>
-      <c r="P101" s="11"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="10"/>
-      <c r="B102" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C102" s="13"/>
-      <c r="D102" s="13"/>
-      <c r="E102" s="13"/>
-      <c r="F102" s="13"/>
-      <c r="G102" s="13"/>
-      <c r="H102" s="13"/>
-      <c r="I102" s="13"/>
-      <c r="J102" s="13"/>
-      <c r="K102" s="10"/>
-      <c r="L102" s="11"/>
-      <c r="M102" s="11"/>
-      <c r="N102" s="11"/>
-      <c r="O102" s="11"/>
-      <c r="P102" s="11"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="10"/>
-      <c r="B103" s="13"/>
-      <c r="C103" s="13"/>
-      <c r="D103" s="13"/>
-      <c r="E103" s="13"/>
-      <c r="F103" s="13"/>
-      <c r="G103" s="13"/>
-      <c r="H103" s="13"/>
-      <c r="I103" s="13"/>
-      <c r="J103" s="13"/>
-      <c r="K103" s="10"/>
-      <c r="L103" s="11"/>
-      <c r="M103" s="11"/>
-      <c r="N103" s="11"/>
-      <c r="O103" s="11"/>
-      <c r="P103" s="11"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="10"/>
-      <c r="B104" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C104" s="10"/>
-      <c r="D104" s="10"/>
-      <c r="E104" s="10"/>
-      <c r="F104" s="10"/>
-      <c r="G104" s="10"/>
-      <c r="H104" s="10"/>
-      <c r="I104" s="10"/>
-      <c r="J104" s="10"/>
-      <c r="K104" s="10"/>
-      <c r="L104" s="11"/>
-      <c r="M104" s="11"/>
-      <c r="N104" s="11"/>
-      <c r="O104" s="11"/>
-      <c r="P104" s="11"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="10"/>
-      <c r="B105" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C105" s="10"/>
-      <c r="D105" s="10"/>
-      <c r="E105" s="10"/>
-      <c r="F105" s="10"/>
-      <c r="G105" s="10"/>
-      <c r="H105" s="10"/>
-      <c r="I105" s="10"/>
-      <c r="J105" s="10"/>
-      <c r="K105" s="10"/>
-      <c r="L105" s="11"/>
-      <c r="M105" s="11"/>
-      <c r="N105" s="11"/>
-      <c r="O105" s="11"/>
-      <c r="P105" s="11"/>
+      <c r="C105" s="8"/>
+      <c r="D105" s="8"/>
+      <c r="E105" s="8"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="8"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="8"/>
+      <c r="J105" s="8"/>
+      <c r="K105" s="8"/>
+      <c r="L105" s="10"/>
+      <c r="M105" s="10"/>
+      <c r="N105" s="10"/>
+      <c r="O105" s="10"/>
+      <c r="P105" s="10"/>
     </row>
     <row r="106" ht="14.25">
-      <c r="A106" s="10"/>
-      <c r="B106" s="10"/>
-      <c r="C106" s="10"/>
-      <c r="D106" s="10"/>
-      <c r="E106" s="10"/>
-      <c r="F106" s="10"/>
-      <c r="G106" s="10"/>
-      <c r="H106" s="10"/>
-      <c r="I106" s="10"/>
-      <c r="J106" s="10"/>
-      <c r="K106" s="10"/>
-      <c r="L106" s="11"/>
-      <c r="M106" s="11"/>
-      <c r="N106" s="11"/>
-      <c r="O106" s="11"/>
-      <c r="P106" s="11"/>
+      <c r="A106" s="8"/>
+      <c r="B106" s="8"/>
+      <c r="C106" s="8"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="8"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="8"/>
+      <c r="J106" s="8"/>
+      <c r="K106" s="8"/>
+      <c r="L106" s="10"/>
+      <c r="M106" s="10"/>
+      <c r="N106" s="10"/>
+      <c r="O106" s="10"/>
+      <c r="P106" s="10"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -6902,7 +6997,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" customWidth="1" min="1" max="1" width="16.81640625"/>
     <col bestFit="1" customWidth="1" min="2" max="2" width="12.1796875"/>
@@ -6912,44 +7007,100 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" ht="128.25">
+      <c r="A2" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="2" ht="130.5">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>254</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>255</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D2" s="3" t="s">
+    </row>
+    <row r="3" ht="57">
+      <c r="A3" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="3" ht="58">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C3" t="s">
-        <v>256</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    </row>
+    <row r="4" ht="128.25">
+      <c r="A4" s="10" t="s">
         <v>259</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" ht="71.25">
+      <c r="A5" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="6" ht="128.25">
+      <c r="A6" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="7" ht="57">
+      <c r="A7" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -6970,12 +7121,12 @@
     <col bestFit="1" customWidth="1" min="4" max="4" width="43"/>
   </cols>
   <sheetData>
-    <row r="1" s="14" customFormat="1">
+    <row r="1" s="13" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -6993,10 +7144,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="D2" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3">
@@ -7008,10 +7159,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4">
@@ -7023,10 +7174,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5">
@@ -7038,10 +7189,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6">
@@ -7053,10 +7204,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7">
@@ -7068,10 +7219,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D7" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8">
@@ -7083,10 +7234,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D8" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9">
@@ -7098,14 +7249,14 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
+      <c r="A10" s="8" t="s">
         <v>139</v>
       </c>
       <c r="B10" t="str">
@@ -7113,14 +7264,14 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
+      <c r="A11" s="8" t="s">
         <v>139</v>
       </c>
       <c r="B11" t="str">
@@ -7128,14 +7279,14 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s">
+      <c r="A12" s="8" t="s">
         <v>139</v>
       </c>
       <c r="B12" t="str">
@@ -7143,166 +7294,166 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B13" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C13" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D13" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B14" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C14" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="D14" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B15" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C15" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="D15" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B16" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C16" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D16" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B17" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C17" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D17" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B18" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C18" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D18" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B19" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C19" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="D19" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B20" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C20" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B21" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C21" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="D21" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="B22" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>299</v>
+        <v>232</v>
       </c>
       <c r="B23" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24">
@@ -7314,10 +7465,10 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="D24" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25">
@@ -7329,10 +7480,10 @@
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="D25" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="26">
@@ -7344,10 +7495,10 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="D26" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27">
@@ -7359,10 +7510,10 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="D27" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="28">
@@ -7374,13 +7525,13 @@
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="D28" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="E28" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29">
@@ -7392,10 +7543,10 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="D29" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30">
@@ -7407,10 +7558,10 @@
         <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D30" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31">
@@ -7422,15 +7573,15 @@
         <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D31" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B32" t="str">
         <f>"1"</f>
@@ -7447,7 +7598,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B33" t="str">
         <f>"2"</f>
@@ -7464,7 +7615,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B34" t="str">
         <f>"3"</f>
@@ -7481,557 +7632,787 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B35" t="str">
         <f>"77"</f>
         <v>77</v>
       </c>
       <c r="C35" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="D35" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B36" t="str">
         <f>"33"</f>
         <v>33</v>
       </c>
       <c r="C36" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D36" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B37" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="D37" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B38" t="str">
         <f>"88888"</f>
         <v>88888</v>
       </c>
       <c r="C38" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="D38" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B39" t="str">
         <f>"77777"</f>
         <v>77777</v>
       </c>
       <c r="C39" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D39" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B40" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="D40" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B41" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="D41" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B42" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="D42" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B43" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="D43" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B44" t="str">
         <f>"7"</f>
         <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D44" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B45" t="str">
         <f>"15"</f>
         <v>15</v>
       </c>
       <c r="C45" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="D45" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B46" t="str">
         <f>"8"</f>
         <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="D46" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B47" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="D47" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B48" t="str">
         <f>"11"</f>
         <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="D48" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B49" t="str">
         <f>"12"</f>
         <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="D49" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B50" t="str">
         <f>"13"</f>
         <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D50" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B51" t="str">
         <f>"14"</f>
         <v>14</v>
       </c>
       <c r="C51" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="D51" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2"/>
+      <c r="A52" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B52" s="10" t="str">
+        <f>"1"</f>
+        <v>1</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="2"/>
+      <c r="A53" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B53" s="10" t="str">
+        <f>"2"</f>
+        <v>2</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="2"/>
+      <c r="A54" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B54" s="10" t="str">
+        <f>"3"</f>
+        <v>3</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="2"/>
+      <c r="A55" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B55" s="10" t="str">
+        <f>"4"</f>
+        <v>4</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="2"/>
+      <c r="A56" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B56" s="10" t="str">
+        <f>"5"</f>
+        <v>5</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="2"/>
+      <c r="A57" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B57" s="10" t="str">
+        <f>"6"</f>
+        <v>6</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="2"/>
+      <c r="A58" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B58" s="10" t="str">
+        <f>"7"</f>
+        <v>7</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="2"/>
+      <c r="A59" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B59" s="10" t="str">
+        <f>"8"</f>
+        <v>8</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="2"/>
-      <c r="D60" s="2"/>
+      <c r="A60" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B60" s="10" t="str">
+        <f>"9"</f>
+        <v>9</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="61" ht="14.25">
+      <c r="A61" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B61" s="10" t="str">
+        <f>"10"</f>
+        <v>10</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="62" ht="15">
-      <c r="B62" s="15"/>
+      <c r="A62" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B62" s="10" t="str">
+        <f>"11"</f>
+        <v>11</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="63" ht="15">
-      <c r="B63" s="15"/>
+      <c r="A63" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B63" s="10" t="str">
+        <f>"12"</f>
+        <v>12</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="64" ht="15">
-      <c r="B64" s="15"/>
+      <c r="A64" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B64" s="10" t="str">
+        <f>"13"</f>
+        <v>13</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="65">
-      <c r="B65" s="15"/>
+      <c r="A65" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B65" s="10" t="str">
+        <f>"14"</f>
+        <v>14</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>352</v>
+      </c>
     </row>
     <row r="66">
-      <c r="B66" s="15"/>
+      <c r="A66" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B66" s="10" t="str">
+        <f>"15"</f>
+        <v>15</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="67">
-      <c r="B67" s="15"/>
+      <c r="A67" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B67" s="10" t="str">
+        <f>"16"</f>
+        <v>16</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="68">
-      <c r="B68" s="15"/>
+      <c r="A68" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B68" s="10" t="str">
+        <f>"17"</f>
+        <v>17</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="69">
-      <c r="B69" s="15"/>
+      <c r="A69" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B69" s="10" t="str">
+        <f>"18"</f>
+        <v>18</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="70">
-      <c r="B70" s="15"/>
+      <c r="A70" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B70" s="10" t="str">
+        <f>"77"</f>
+        <v>77</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="71">
-      <c r="B71" s="15"/>
+      <c r="B71" s="14"/>
     </row>
     <row r="72">
-      <c r="B72" s="15"/>
+      <c r="B72" s="14"/>
     </row>
     <row r="73">
-      <c r="B73" s="15"/>
+      <c r="B73" s="14"/>
     </row>
     <row r="74">
-      <c r="B74" s="15"/>
+      <c r="B74" s="14"/>
     </row>
     <row r="75">
-      <c r="B75" s="15"/>
+      <c r="B75" s="14"/>
     </row>
     <row r="76">
-      <c r="B76" s="15"/>
+      <c r="B76" s="14"/>
     </row>
     <row r="77">
-      <c r="B77" s="15"/>
+      <c r="B77" s="14"/>
     </row>
     <row r="78">
-      <c r="B78" s="15"/>
+      <c r="B78" s="14"/>
     </row>
     <row r="79">
-      <c r="B79" s="15"/>
+      <c r="B79" s="14"/>
     </row>
     <row r="80">
-      <c r="B80" s="15"/>
+      <c r="B80" s="14"/>
     </row>
     <row r="81">
-      <c r="B81" s="15"/>
+      <c r="B81" s="14"/>
     </row>
     <row r="82">
-      <c r="B82" s="15"/>
+      <c r="B82" s="14"/>
     </row>
     <row r="83">
-      <c r="B83" s="15"/>
+      <c r="B83" s="14"/>
     </row>
     <row r="84">
-      <c r="B84" s="15"/>
+      <c r="B84" s="14"/>
     </row>
     <row r="85">
-      <c r="B85" s="15"/>
+      <c r="B85" s="14"/>
     </row>
     <row r="86">
-      <c r="B86" s="15"/>
+      <c r="B86" s="14"/>
     </row>
     <row r="87">
-      <c r="B87" s="15"/>
+      <c r="B87" s="14"/>
     </row>
     <row r="88">
-      <c r="B88" s="15"/>
+      <c r="B88" s="14"/>
     </row>
     <row r="89">
-      <c r="B89" s="15"/>
+      <c r="B89" s="14"/>
     </row>
     <row r="90">
-      <c r="B90" s="15"/>
+      <c r="B90" s="14"/>
     </row>
     <row r="91">
-      <c r="B91" s="15"/>
+      <c r="B91" s="14"/>
     </row>
     <row r="92">
-      <c r="B92" s="15"/>
+      <c r="B92" s="14"/>
     </row>
     <row r="93">
-      <c r="B93" s="15"/>
-      <c r="C93" s="15"/>
+      <c r="B93" s="14"/>
+      <c r="C93" s="14"/>
     </row>
     <row r="94">
-      <c r="B94" s="15"/>
-      <c r="C94" s="15"/>
+      <c r="B94" s="14"/>
+      <c r="C94" s="14"/>
     </row>
     <row r="95">
-      <c r="B95" s="15"/>
-      <c r="C95" s="15"/>
+      <c r="B95" s="14"/>
+      <c r="C95" s="14"/>
     </row>
     <row r="96">
-      <c r="B96" s="15"/>
-      <c r="C96" s="15"/>
+      <c r="B96" s="14"/>
+      <c r="C96" s="14"/>
     </row>
     <row r="97">
-      <c r="B97" s="15"/>
-      <c r="C97" s="15"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="14"/>
     </row>
     <row r="98">
-      <c r="B98" s="15"/>
-      <c r="C98" s="15"/>
+      <c r="B98" s="14"/>
+      <c r="C98" s="14"/>
     </row>
     <row r="99">
-      <c r="B99" s="15"/>
-      <c r="C99" s="15"/>
+      <c r="B99" s="14"/>
+      <c r="C99" s="14"/>
     </row>
     <row r="100">
-      <c r="C100" s="15"/>
+      <c r="C100" s="14"/>
     </row>
     <row r="101">
-      <c r="B101" s="15"/>
-      <c r="C101" s="15"/>
+      <c r="B101" s="14"/>
+      <c r="C101" s="14"/>
     </row>
     <row r="102">
-      <c r="B102" s="15"/>
-      <c r="C102" s="15"/>
+      <c r="B102" s="14"/>
+      <c r="C102" s="14"/>
     </row>
     <row r="103">
-      <c r="B103" s="15"/>
-      <c r="C103" s="15"/>
+      <c r="B103" s="14"/>
+      <c r="C103" s="14"/>
     </row>
     <row r="104">
-      <c r="B104" s="15"/>
-      <c r="C104" s="15"/>
+      <c r="B104" s="14"/>
+      <c r="C104" s="14"/>
     </row>
     <row r="105">
-      <c r="B105" s="15"/>
-      <c r="C105" s="15"/>
+      <c r="B105" s="14"/>
+      <c r="C105" s="14"/>
     </row>
     <row r="106">
-      <c r="B106" s="15"/>
-      <c r="C106" s="15"/>
+      <c r="B106" s="14"/>
+      <c r="C106" s="14"/>
     </row>
     <row r="107">
-      <c r="B107" s="15"/>
-      <c r="C107" s="15"/>
+      <c r="B107" s="14"/>
+      <c r="C107" s="14"/>
     </row>
     <row r="108">
-      <c r="B108" s="15"/>
-      <c r="C108" s="15"/>
+      <c r="B108" s="14"/>
+      <c r="C108" s="14"/>
     </row>
     <row r="109">
-      <c r="B109" s="15"/>
-      <c r="C109" s="15"/>
+      <c r="B109" s="14"/>
+      <c r="C109" s="14"/>
     </row>
     <row r="110">
-      <c r="B110" s="15"/>
-      <c r="C110" s="15"/>
+      <c r="B110" s="14"/>
+      <c r="C110" s="14"/>
     </row>
     <row r="111">
-      <c r="B111" s="15"/>
-      <c r="C111" s="15"/>
+      <c r="B111" s="14"/>
+      <c r="C111" s="14"/>
     </row>
     <row r="112">
-      <c r="B112" s="15"/>
-      <c r="C112" s="15"/>
+      <c r="B112" s="14"/>
+      <c r="C112" s="14"/>
     </row>
     <row r="113">
-      <c r="B113" s="15"/>
-      <c r="C113" s="15"/>
+      <c r="B113" s="14"/>
+      <c r="C113" s="14"/>
     </row>
     <row r="114">
-      <c r="B114" s="15"/>
-      <c r="C114" s="15"/>
+      <c r="B114" s="14"/>
+      <c r="C114" s="14"/>
     </row>
     <row r="115">
-      <c r="B115" s="15"/>
-      <c r="C115" s="15"/>
+      <c r="B115" s="14"/>
+      <c r="C115" s="14"/>
     </row>
     <row r="116">
-      <c r="B116" s="15"/>
-      <c r="C116" s="15"/>
+      <c r="B116" s="14"/>
+      <c r="C116" s="14"/>
     </row>
     <row r="117">
-      <c r="B117" s="15"/>
-      <c r="C117" s="15"/>
+      <c r="B117" s="14"/>
+      <c r="C117" s="14"/>
     </row>
     <row r="118">
-      <c r="B118" s="15"/>
-      <c r="C118" s="15"/>
+      <c r="B118" s="14"/>
+      <c r="C118" s="14"/>
     </row>
     <row r="119">
-      <c r="B119" s="15"/>
+      <c r="B119" s="14"/>
     </row>
     <row r="120">
-      <c r="B120" s="15"/>
+      <c r="B120" s="14"/>
     </row>
     <row r="121">
-      <c r="B121" s="15"/>
+      <c r="B121" s="14"/>
     </row>
     <row r="122">
-      <c r="B122" s="15"/>
+      <c r="B122" s="14"/>
     </row>
     <row r="123">
-      <c r="B123" s="15"/>
+      <c r="B123" s="14"/>
     </row>
     <row r="124">
-      <c r="B124" s="15"/>
+      <c r="B124" s="14"/>
     </row>
     <row r="125">
-      <c r="B125" s="15"/>
+      <c r="B125" s="14"/>
     </row>
     <row r="127">
-      <c r="B127" s="15"/>
+      <c r="B127" s="14"/>
     </row>
     <row r="128">
-      <c r="B128" s="15"/>
+      <c r="B128" s="14"/>
     </row>
     <row r="129">
-      <c r="B129" s="15"/>
+      <c r="B129" s="14"/>
     </row>
     <row r="130">
-      <c r="B130" s="15"/>
+      <c r="B130" s="14"/>
     </row>
     <row r="131">
-      <c r="B131" s="15"/>
+      <c r="B131" s="14"/>
     </row>
     <row r="132">
-      <c r="B132" s="15"/>
+      <c r="B132" s="14"/>
     </row>
     <row r="133">
-      <c r="B133" s="15"/>
+      <c r="B133" s="14"/>
     </row>
     <row r="134">
-      <c r="B134" s="15"/>
+      <c r="B134" s="14"/>
     </row>
     <row r="135">
-      <c r="B135" s="15"/>
+      <c r="B135" s="14"/>
     </row>
     <row r="136">
-      <c r="B136" s="15"/>
+      <c r="B136" s="14"/>
     </row>
     <row r="137">
-      <c r="B137" s="15"/>
+      <c r="B137" s="14"/>
     </row>
     <row r="138">
-      <c r="B138" s="15"/>
+      <c r="B138" s="14"/>
     </row>
     <row r="139">
-      <c r="B139" s="15"/>
+      <c r="B139" s="14"/>
     </row>
     <row r="140">
-      <c r="B140" s="15"/>
+      <c r="B140" s="14"/>
     </row>
     <row r="141">
-      <c r="B141" s="15"/>
+      <c r="B141" s="14"/>
     </row>
     <row r="142">
-      <c r="B142" s="15"/>
+      <c r="B142" s="14"/>
     </row>
     <row r="143">
-      <c r="B143" s="15"/>
+      <c r="B143" s="14"/>
     </row>
     <row r="144">
-      <c r="B144" s="15"/>
+      <c r="B144" s="14"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -8050,75 +8431,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1" s="16" t="s">
+      <c r="A1" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" s="12" customFormat="1">
-      <c r="A2" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="3" s="12" customFormat="1">
-      <c r="A3" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="4" s="12" customFormat="1">
-      <c r="A4" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="5" s="12" customFormat="1">
-      <c r="A5" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="6" s="12" customFormat="1">
-      <c r="A6" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="7" s="12" customFormat="1">
-      <c r="A7" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>344</v>
+    <row r="2" s="11" customFormat="1">
+      <c r="A2" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="3" s="11" customFormat="1">
+      <c r="A3" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="4" s="11" customFormat="1">
+      <c r="A4" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="5" s="11" customFormat="1">
+      <c r="A5" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="6" s="11" customFormat="1">
+      <c r="A6" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="7" s="11" customFormat="1">
+      <c r="A7" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>345</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>346</v>
+        <v>370</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>347</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>348</v>
+        <v>372</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -8141,16 +8522,16 @@
   <sheetData>
     <row r="1" s="7" customFormat="1">
       <c r="A1" s="7" t="s">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>351</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
@@ -8158,13 +8539,13 @@
         <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="C2" t="s">
-        <v>352</v>
+        <v>377</v>
       </c>
       <c r="D2" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -8192,10 +8573,10 @@
         <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>351</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1">
@@ -8209,7 +8590,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>355</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1">
@@ -8389,7 +8770,7 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>356</v>
+        <v>381</v>
       </c>
     </row>
     <row r="20">
@@ -8438,7 +8819,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="B24" t="s">
         <v>150</v>
@@ -8449,7 +8830,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>358</v>
+        <v>383</v>
       </c>
       <c r="B25" t="s">
         <v>150</v>
@@ -8460,7 +8841,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>359</v>
+        <v>384</v>
       </c>
       <c r="B26" t="s">
         <v>150</v>
@@ -8471,10 +8852,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="B27" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C27" t="b">
         <v>0</v>
@@ -8482,10 +8863,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="B28" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C28" t="b">
         <v>0</v>
@@ -8493,10 +8874,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="B29" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C29" t="b">
         <v>0</v>
@@ -8504,10 +8885,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>363</v>
+        <v>388</v>
       </c>
       <c r="B30" t="s">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="C30" t="b">
         <v>0</v>
@@ -8515,7 +8896,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="B31" t="s">
         <v>150</v>
@@ -8526,10 +8907,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>366</v>
+        <v>391</v>
       </c>
       <c r="B32" t="s">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
@@ -8537,7 +8918,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>367</v>
+        <v>392</v>
       </c>
       <c r="B33" t="s">
         <v>150</v>
@@ -8548,10 +8929,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="B34" t="s">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
@@ -8559,7 +8940,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="B35" t="s">
         <v>150</v>
@@ -8570,10 +8951,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>370</v>
+        <v>395</v>
       </c>
       <c r="B36" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C36" t="b">
         <v>0</v>
@@ -8581,10 +8962,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="B37" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C37" t="b">
         <v>0</v>
@@ -8592,10 +8973,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="B38" t="s">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="C38" t="b">
         <v>0</v>
@@ -8603,7 +8984,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="B39" t="s">
         <v>156</v>
@@ -8614,7 +8995,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="B40" t="s">
         <v>156</v>
@@ -8625,7 +9006,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="B41" t="s">
         <v>156</v>
@@ -8636,7 +9017,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="B42" t="s">
         <v>61</v>
@@ -8647,7 +9028,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="B43" t="s">
         <v>61</v>
@@ -8658,7 +9039,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="B44" t="s">
         <v>61</v>
@@ -8669,7 +9050,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="B45" t="s">
         <v>61</v>
@@ -8691,10 +9072,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="B47" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C47" t="b">
         <v>0</v>
@@ -8702,7 +9083,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="B48" t="s">
         <v>61</v>
@@ -8713,10 +9094,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="B49" t="s">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="C49" t="b">
         <v>0</v>
@@ -8724,10 +9105,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="B50" t="s">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="C50" t="b">
         <v>1</v>
@@ -8737,10 +9118,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="B51" t="s">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="C51" t="b">
         <v>1</v>
@@ -8750,10 +9131,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>386</v>
+        <v>411</v>
       </c>
       <c r="B52" t="s">
-        <v>364</v>
+        <v>389</v>
       </c>
       <c r="C52" t="b">
         <v>1</v>
@@ -8761,10 +9142,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="B53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C53" t="b">
         <v>0</v>
@@ -8772,7 +9153,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="B54" t="s">
         <v>61</v>
@@ -8783,10 +9164,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="B55" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C55" t="b">
         <v>0</v>
@@ -8794,7 +9175,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="B56" t="s">
         <v>150</v>
@@ -8816,7 +9197,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>156</v>
@@ -8825,12 +9206,12 @@
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>393</v>
+        <v>418</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>156</v>
@@ -8841,7 +9222,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>156</v>
@@ -8852,7 +9233,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
       <c r="B62" t="s">
         <v>47</v>
@@ -8863,7 +9244,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="B63" t="s">
         <v>47</v>
@@ -8874,7 +9255,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="B64" t="s">
         <v>156</v>
@@ -8885,7 +9266,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>398</v>
+        <v>423</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>156</v>
@@ -8896,7 +9277,7 @@
     </row>
     <row r="66" s="2" customFormat="1">
       <c r="A66" s="2" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>156</v>
@@ -8907,10 +9288,10 @@
     </row>
     <row r="67" s="2" customFormat="1">
       <c r="A67" s="2" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C67" s="2" t="b">
         <v>0</v>
@@ -8918,10 +9299,10 @@
     </row>
     <row r="68" s="2" customFormat="1">
       <c r="A68" t="s">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="B68" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C68" t="b">
         <v>0</v>
@@ -8929,10 +9310,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>402</v>
+        <v>427</v>
       </c>
       <c r="B69" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C69" t="b">
         <v>0</v>
@@ -8940,10 +9321,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="B70" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C70" t="b">
         <v>0</v>
@@ -8951,7 +9332,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="B71" t="s">
         <v>61</v>
@@ -8962,10 +9343,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="B72" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C72" t="b">
         <v>0</v>
@@ -8973,10 +9354,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="B73" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C73" t="b">
         <v>0</v>
@@ -8984,10 +9365,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C74" t="b">
         <v>0</v>
@@ -8995,7 +9376,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>156</v>
@@ -9006,7 +9387,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>156</v>
@@ -9017,7 +9398,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>156</v>
@@ -9028,14 +9409,12 @@
     </row>
     <row r="79" ht="14.25">
       <c r="A79" t="s">
-        <v>411</v>
-      </c>
-      <c r="B79"/>
-      <c r="D79"/>
+        <v>436</v>
+      </c>
     </row>
     <row r="80" ht="14.25">
       <c r="A80" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B80" t="s">
         <v>169</v>
@@ -9046,7 +9425,7 @@
     </row>
     <row r="81" ht="14.25">
       <c r="A81" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B81" t="s">
         <v>150</v>
@@ -9057,7 +9436,7 @@
     </row>
     <row r="82" ht="14.25">
       <c r="A82" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B82" t="s">
         <v>61</v>
@@ -9068,7 +9447,7 @@
     </row>
     <row r="83" ht="14.25">
       <c r="A83" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B83" t="s">
         <v>150</v>
@@ -9079,7 +9458,7 @@
     </row>
     <row r="84" ht="14.25">
       <c r="A84" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B84" t="s">
         <v>61</v>
@@ -9090,10 +9469,10 @@
     </row>
     <row r="85" ht="14.25">
       <c r="A85" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B85" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C85" t="b">
         <v>0</v>
@@ -9101,7 +9480,7 @@
     </row>
     <row r="86" ht="14.25">
       <c r="A86" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B86" t="s">
         <v>61</v>
@@ -9112,10 +9491,10 @@
     </row>
     <row r="87" ht="14.25">
       <c r="A87" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B87" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C87" t="b">
         <v>0</v>
@@ -9123,7 +9502,7 @@
     </row>
     <row r="88" ht="14.25">
       <c r="A88" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B88" t="s">
         <v>61</v>
@@ -9134,10 +9513,10 @@
     </row>
     <row r="89" ht="14.25">
       <c r="A89" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B89" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C89" t="b">
         <v>0</v>
@@ -9145,7 +9524,7 @@
     </row>
     <row r="90" ht="14.25">
       <c r="A90" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B90" t="s">
         <v>61</v>
@@ -9156,7 +9535,7 @@
     </row>
     <row r="91" ht="14.25">
       <c r="A91" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B91" t="s">
         <v>150</v>
@@ -9167,7 +9546,7 @@
     </row>
     <row r="92" ht="14.25">
       <c r="A92" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B92" t="s">
         <v>61</v>
@@ -9178,7 +9557,7 @@
     </row>
     <row r="93" ht="14.25">
       <c r="A93" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B93" t="s">
         <v>150</v>
@@ -9189,7 +9568,7 @@
     </row>
     <row r="94" ht="14.25">
       <c r="A94" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B94" t="s">
         <v>61</v>
@@ -9200,7 +9579,7 @@
     </row>
     <row r="95" ht="14.25">
       <c r="A95" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B95" t="s">
         <v>150</v>
@@ -9211,7 +9590,7 @@
     </row>
     <row r="96" ht="14.25">
       <c r="A96" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B96" t="s">
         <v>61</v>
@@ -9222,10 +9601,10 @@
     </row>
     <row r="97" ht="14.25">
       <c r="A97" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B97" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C97" t="b">
         <v>0</v>
@@ -9233,7 +9612,7 @@
     </row>
     <row r="98" ht="14.25">
       <c r="A98" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B98" t="s">
         <v>150</v>
@@ -9244,7 +9623,7 @@
     </row>
     <row r="99" ht="14.25">
       <c r="A99" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B99" t="s">
         <v>61</v>
@@ -9255,7 +9634,7 @@
     </row>
     <row r="100" ht="14.25">
       <c r="A100" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B100" t="s">
         <v>150</v>
@@ -9266,10 +9645,10 @@
     </row>
     <row r="101" ht="14.25">
       <c r="A101" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B101" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C101" t="b">
         <v>0</v>
@@ -9277,7 +9656,7 @@
     </row>
     <row r="102" ht="14.25">
       <c r="A102" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B102" t="s">
         <v>61</v>
@@ -9288,7 +9667,7 @@
     </row>
     <row r="103" ht="14.25">
       <c r="A103" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B103" t="s">
         <v>61</v>
@@ -9299,7 +9678,7 @@
     </row>
     <row r="104" ht="14.25">
       <c r="A104" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B104" t="s">
         <v>150</v>
@@ -9310,7 +9689,7 @@
     </row>
     <row r="105" ht="14.25">
       <c r="A105" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B105" t="s">
         <v>150</v>
@@ -9321,20 +9700,16 @@
     </row>
     <row r="106" ht="14.25">
       <c r="A106" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B106" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C106" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="107" ht="14.25">
-      <c r="A107"/>
-      <c r="B107"/>
-      <c r="C107"/>
-    </row>
+    <row r="107" ht="14.25"/>
     <row r="108" ht="14.25"/>
     <row r="109" ht="14.25"/>
     <row r="110" ht="14.25"/>

--- a/app/config/tables/MADTRIAL_FU_PHONE/Forms/MADTRIAL_FU_PHONE/MADTRIAL_FU_PHONE.xlsx
+++ b/app/config/tables/MADTRIAL_FU_PHONE/Forms/MADTRIAL_FU_PHONE/MADTRIAL_FU_PHONE.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="403">
   <si>
     <t>setting_name</t>
   </si>
@@ -1208,108 +1208,6 @@
   </si>
   <si>
     <t>FU</t>
-  </si>
-  <si>
-    <t>HOSPALTA1</t>
-  </si>
-  <si>
-    <t>HOSPALTA2</t>
-  </si>
-  <si>
-    <t>HOSPALTA3</t>
-  </si>
-  <si>
-    <t>HOSPCAUSA1</t>
-  </si>
-  <si>
-    <t>HOSPCAUSA2</t>
-  </si>
-  <si>
-    <t>HOSPCAUSA3</t>
-  </si>
-  <si>
-    <t>HOSPCODE1</t>
-  </si>
-  <si>
-    <t>select_one_dropdown</t>
-  </si>
-  <si>
-    <t>hospcode1ns</t>
-  </si>
-  <si>
-    <t>HOSPCODE2</t>
-  </si>
-  <si>
-    <t>hospcode2ns</t>
-  </si>
-  <si>
-    <t>HOSPCODE3</t>
-  </si>
-  <si>
-    <t>hospcode3ns</t>
-  </si>
-  <si>
-    <t>HOSPDATA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adate </t>
-  </si>
-  <si>
-    <t>HOSPDATA2</t>
-  </si>
-  <si>
-    <t>HOSPDATA3</t>
-  </si>
-  <si>
-    <t>HOSPDIAS1</t>
-  </si>
-  <si>
-    <t>HOSPDIAS2</t>
-  </si>
-  <si>
-    <t>HOSPDIAS3</t>
-  </si>
-  <si>
-    <t>HOSPI</t>
-  </si>
-  <si>
-    <t>HOSPI2</t>
-  </si>
-  <si>
-    <t>HOSPI3</t>
-  </si>
-  <si>
-    <t>HOSPIVEZ</t>
-  </si>
-  <si>
-    <t>MORNOME</t>
-  </si>
-  <si>
-    <t>PODEAUT</t>
-  </si>
-  <si>
-    <t>REG</t>
-  </si>
-  <si>
-    <t>reghosp1</t>
-  </si>
-  <si>
-    <t>reghosp2</t>
-  </si>
-  <si>
-    <t>reghosp3</t>
-  </si>
-  <si>
-    <t>TABNOME</t>
-  </si>
-  <si>
-    <t>VACHIS</t>
-  </si>
-  <si>
-    <t>VACOUTRO</t>
-  </si>
-  <si>
-    <t>VACTIPO</t>
   </si>
   <si>
     <t>chamada1</t>
@@ -1471,7 +1369,7 @@
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
@@ -1492,6 +1390,9 @@
     <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Excel Built-in Normal" xfId="1"/>
@@ -8758,27 +8659,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1"/>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" t="b">
-        <v>1</v>
-      </c>
-      <c r="D19" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>144</v>
-      </c>
-      <c r="B20" t="s">
-        <v>47</v>
+    <row r="18" s="2" customFormat="1">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+    </row>
+    <row r="19" s="2" customFormat="1">
+      <c r="A19" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1">
+      <c r="A20" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>150</v>
       </c>
       <c r="C20" t="b">
         <v>0</v>
@@ -8786,21 +8688,24 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>156</v>
+        <v>47</v>
       </c>
       <c r="C21" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="B22" t="s">
-        <v>156</v>
+        <v>47</v>
       </c>
       <c r="C22" t="b">
         <v>0</v>
@@ -8808,21 +8713,21 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B23" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>382</v>
+        <v>160</v>
       </c>
       <c r="B24" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C24" t="b">
         <v>0</v>
@@ -8830,65 +8735,58 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>383</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s">
         <v>150</v>
       </c>
       <c r="C25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>384</v>
-      </c>
-      <c r="B26" t="s">
-        <v>150</v>
-      </c>
-      <c r="C26" t="b">
-        <v>0</v>
-      </c>
-    </row>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25"/>
     <row r="27">
       <c r="A27" t="s">
-        <v>385</v>
-      </c>
-      <c r="B27" t="s">
-        <v>219</v>
-      </c>
-      <c r="C27" t="b">
-        <v>0</v>
+        <v>382</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>386</v>
-      </c>
-      <c r="B28" t="s">
-        <v>219</v>
-      </c>
-      <c r="C28" t="b">
-        <v>0</v>
+        <v>384</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C28" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>387</v>
-      </c>
-      <c r="B29" t="s">
-        <v>219</v>
-      </c>
-      <c r="C29" t="b">
-        <v>0</v>
+        <v>385</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B30" t="s">
-        <v>389</v>
+        <v>47</v>
       </c>
       <c r="C30" t="b">
         <v>0</v>
@@ -8896,65 +8794,65 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B31" t="s">
-        <v>150</v>
+        <v>47</v>
       </c>
       <c r="C31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B32" t="s">
-        <v>389</v>
+        <v>156</v>
       </c>
       <c r="C32" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s">
-        <v>392</v>
-      </c>
-      <c r="B33" t="s">
-        <v>150</v>
+      <c r="A33" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="C33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>393</v>
-      </c>
-      <c r="B34" t="s">
-        <v>389</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1">
+      <c r="A34" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="C34" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>394</v>
-      </c>
-      <c r="B35" t="s">
-        <v>150</v>
-      </c>
-      <c r="C35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
+    <row r="35" s="2" customFormat="1">
+      <c r="A35" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C35" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1">
       <c r="A36" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B36" t="s">
-        <v>396</v>
+        <v>219</v>
       </c>
       <c r="C36" t="b">
         <v>0</v>
@@ -8962,10 +8860,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B37" t="s">
-        <v>396</v>
+        <v>219</v>
       </c>
       <c r="C37" t="b">
         <v>0</v>
@@ -8973,10 +8871,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B38" t="s">
-        <v>396</v>
+        <v>219</v>
       </c>
       <c r="C38" t="b">
         <v>0</v>
@@ -8984,10 +8882,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B39" t="s">
-        <v>156</v>
+        <v>61</v>
       </c>
       <c r="C39" t="b">
         <v>0</v>
@@ -8995,10 +8893,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B40" t="s">
-        <v>156</v>
+        <v>219</v>
       </c>
       <c r="C40" t="b">
         <v>0</v>
@@ -9006,10 +8904,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B41" t="s">
-        <v>156</v>
+        <v>219</v>
       </c>
       <c r="C41" t="b">
         <v>0</v>
@@ -9017,143 +8915,123 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>219</v>
       </c>
       <c r="C42" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s">
-        <v>403</v>
-      </c>
-      <c r="B43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" t="b">
+      <c r="A43" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C43" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s">
-        <v>404</v>
-      </c>
-      <c r="B44" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" t="b">
+      <c r="A44" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C44" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s">
-        <v>405</v>
-      </c>
-      <c r="B45" t="s">
-        <v>61</v>
-      </c>
-      <c r="C45" t="b">
+      <c r="A45" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C45" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>136</v>
-      </c>
-      <c r="B46" t="s">
-        <v>40</v>
-      </c>
-      <c r="C46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
+    <row r="46" ht="14.25"/>
+    <row r="47" ht="14.25">
       <c r="A47" t="s">
-        <v>406</v>
-      </c>
-      <c r="B47" t="s">
-        <v>219</v>
-      </c>
-      <c r="C47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25">
       <c r="A48" t="s">
-        <v>407</v>
+        <v>170</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>169</v>
       </c>
       <c r="C48" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="14.25">
       <c r="A49" t="s">
-        <v>408</v>
+        <v>175</v>
       </c>
       <c r="B49" t="s">
-        <v>389</v>
+        <v>150</v>
       </c>
       <c r="C49" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="14.25">
       <c r="A50" t="s">
-        <v>409</v>
+        <v>179</v>
       </c>
       <c r="B50" t="s">
-        <v>389</v>
+        <v>61</v>
       </c>
       <c r="C50" t="b">
-        <v>1</v>
-      </c>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-    </row>
-    <row r="51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25">
       <c r="A51" t="s">
-        <v>410</v>
+        <v>183</v>
       </c>
       <c r="B51" t="s">
-        <v>389</v>
+        <v>150</v>
       </c>
       <c r="C51" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-    </row>
-    <row r="52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="14.25">
       <c r="A52" t="s">
-        <v>411</v>
+        <v>184</v>
       </c>
       <c r="B52" t="s">
-        <v>389</v>
+        <v>61</v>
       </c>
       <c r="C52" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="14.25">
       <c r="A53" t="s">
-        <v>412</v>
+        <v>189</v>
       </c>
       <c r="B53" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="C53" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="14.25">
       <c r="A54" t="s">
-        <v>413</v>
+        <v>190</v>
       </c>
       <c r="B54" t="s">
         <v>61</v>
@@ -9162,155 +9040,163 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="14.25">
       <c r="A55" t="s">
-        <v>414</v>
+        <v>194</v>
       </c>
       <c r="B55" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="C55" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="14.25">
       <c r="A56" t="s">
-        <v>415</v>
+        <v>195</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>61</v>
       </c>
       <c r="C56" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="14.25">
       <c r="A57" t="s">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>188</v>
       </c>
       <c r="C57" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="59">
+    <row r="58" ht="14.25">
+      <c r="A58" t="s">
+        <v>200</v>
+      </c>
+      <c r="B58" t="s">
+        <v>61</v>
+      </c>
+      <c r="C58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="14.25">
       <c r="A59" t="s">
-        <v>416</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C59" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D59" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>204</v>
+      </c>
+      <c r="B59" t="s">
+        <v>150</v>
+      </c>
+      <c r="C59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="14.25">
       <c r="A60" t="s">
-        <v>418</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C60" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>205</v>
+      </c>
+      <c r="B60" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" ht="14.25">
       <c r="A61" t="s">
-        <v>419</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C61" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>209</v>
+      </c>
+      <c r="B61" t="s">
+        <v>150</v>
+      </c>
+      <c r="C61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="14.25">
       <c r="A62" t="s">
-        <v>420</v>
+        <v>210</v>
       </c>
       <c r="B62" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C62" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="14.25">
       <c r="A63" t="s">
-        <v>421</v>
+        <v>214</v>
       </c>
       <c r="B63" t="s">
-        <v>47</v>
+        <v>150</v>
       </c>
       <c r="C63" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="14.25">
       <c r="A64" t="s">
-        <v>422</v>
+        <v>215</v>
       </c>
       <c r="B64" t="s">
-        <v>156</v>
+        <v>61</v>
       </c>
       <c r="C64" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>156</v>
+    <row r="65" ht="14.25">
+      <c r="A65" t="s">
+        <v>220</v>
+      </c>
+      <c r="B65" t="s">
+        <v>219</v>
       </c>
       <c r="C65" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="66" s="2" customFormat="1">
-      <c r="A66" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>156</v>
+    <row r="66" ht="14.25">
+      <c r="A66" t="s">
+        <v>223</v>
+      </c>
+      <c r="B66" t="s">
+        <v>150</v>
       </c>
       <c r="C66" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1">
-      <c r="A67" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C67" s="2" t="b">
+    <row r="67" ht="14.25">
+      <c r="A67" t="s">
+        <v>224</v>
+      </c>
+      <c r="B67" t="s">
+        <v>61</v>
+      </c>
+      <c r="C67" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="68" s="2" customFormat="1">
+    <row r="68" ht="14.25">
       <c r="A68" t="s">
-        <v>426</v>
+        <v>228</v>
       </c>
       <c r="B68" t="s">
-        <v>219</v>
+        <v>150</v>
       </c>
       <c r="C68" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="14.25">
       <c r="A69" t="s">
-        <v>427</v>
+        <v>229</v>
       </c>
       <c r="B69" t="s">
         <v>219</v>
@@ -9319,20 +9205,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="14.25">
       <c r="A70" t="s">
-        <v>428</v>
+        <v>233</v>
       </c>
       <c r="B70" t="s">
-        <v>219</v>
+        <v>61</v>
       </c>
       <c r="C70" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="14.25">
       <c r="A71" t="s">
-        <v>429</v>
+        <v>236</v>
       </c>
       <c r="B71" t="s">
         <v>61</v>
@@ -9341,31 +9227,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="14.25">
       <c r="A72" t="s">
-        <v>430</v>
+        <v>240</v>
       </c>
       <c r="B72" t="s">
-        <v>219</v>
+        <v>150</v>
       </c>
       <c r="C72" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="14.25">
       <c r="A73" t="s">
-        <v>431</v>
+        <v>242</v>
       </c>
       <c r="B73" t="s">
-        <v>219</v>
+        <v>150</v>
       </c>
       <c r="C73" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="14.25">
       <c r="A74" t="s">
-        <v>432</v>
+        <v>246</v>
       </c>
       <c r="B74" t="s">
         <v>219</v>
@@ -9374,352 +9260,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C75" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C76" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C77" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" ht="14.25">
-      <c r="A79" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="80" ht="14.25">
-      <c r="A80" t="s">
-        <v>170</v>
-      </c>
-      <c r="B80" t="s">
-        <v>169</v>
-      </c>
-      <c r="C80" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" ht="14.25">
-      <c r="A81" t="s">
-        <v>175</v>
-      </c>
-      <c r="B81" t="s">
-        <v>150</v>
-      </c>
-      <c r="C81" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" ht="14.25">
-      <c r="A82" t="s">
-        <v>179</v>
-      </c>
-      <c r="B82" t="s">
-        <v>61</v>
-      </c>
-      <c r="C82" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" ht="14.25">
-      <c r="A83" t="s">
-        <v>183</v>
-      </c>
-      <c r="B83" t="s">
-        <v>150</v>
-      </c>
-      <c r="C83" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" ht="14.25">
-      <c r="A84" t="s">
-        <v>184</v>
-      </c>
-      <c r="B84" t="s">
-        <v>61</v>
-      </c>
-      <c r="C84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" ht="14.25">
-      <c r="A85" t="s">
-        <v>189</v>
-      </c>
-      <c r="B85" t="s">
-        <v>188</v>
-      </c>
-      <c r="C85" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" ht="14.25">
-      <c r="A86" t="s">
-        <v>190</v>
-      </c>
-      <c r="B86" t="s">
-        <v>61</v>
-      </c>
-      <c r="C86" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" ht="14.25">
-      <c r="A87" t="s">
-        <v>194</v>
-      </c>
-      <c r="B87" t="s">
-        <v>188</v>
-      </c>
-      <c r="C87" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" ht="14.25">
-      <c r="A88" t="s">
-        <v>195</v>
-      </c>
-      <c r="B88" t="s">
-        <v>61</v>
-      </c>
-      <c r="C88" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" ht="14.25">
-      <c r="A89" t="s">
-        <v>199</v>
-      </c>
-      <c r="B89" t="s">
-        <v>188</v>
-      </c>
-      <c r="C89" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" ht="14.25">
-      <c r="A90" t="s">
-        <v>200</v>
-      </c>
-      <c r="B90" t="s">
-        <v>61</v>
-      </c>
-      <c r="C90" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" ht="14.25">
-      <c r="A91" t="s">
-        <v>204</v>
-      </c>
-      <c r="B91" t="s">
-        <v>150</v>
-      </c>
-      <c r="C91" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" ht="14.25">
-      <c r="A92" t="s">
-        <v>205</v>
-      </c>
-      <c r="B92" t="s">
-        <v>61</v>
-      </c>
-      <c r="C92" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" ht="14.25">
-      <c r="A93" t="s">
-        <v>209</v>
-      </c>
-      <c r="B93" t="s">
-        <v>150</v>
-      </c>
-      <c r="C93" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" ht="14.25">
-      <c r="A94" t="s">
-        <v>210</v>
-      </c>
-      <c r="B94" t="s">
-        <v>61</v>
-      </c>
-      <c r="C94" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" ht="14.25">
-      <c r="A95" t="s">
-        <v>214</v>
-      </c>
-      <c r="B95" t="s">
-        <v>150</v>
-      </c>
-      <c r="C95" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" ht="14.25">
-      <c r="A96" t="s">
-        <v>215</v>
-      </c>
-      <c r="B96" t="s">
-        <v>61</v>
-      </c>
-      <c r="C96" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" ht="14.25">
-      <c r="A97" t="s">
-        <v>220</v>
-      </c>
-      <c r="B97" t="s">
-        <v>219</v>
-      </c>
-      <c r="C97" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" ht="14.25">
-      <c r="A98" t="s">
-        <v>223</v>
-      </c>
-      <c r="B98" t="s">
-        <v>150</v>
-      </c>
-      <c r="C98" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" ht="14.25">
-      <c r="A99" t="s">
-        <v>224</v>
-      </c>
-      <c r="B99" t="s">
-        <v>61</v>
-      </c>
-      <c r="C99" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" ht="14.25">
-      <c r="A100" t="s">
-        <v>228</v>
-      </c>
-      <c r="B100" t="s">
-        <v>150</v>
-      </c>
-      <c r="C100" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" ht="14.25">
-      <c r="A101" t="s">
-        <v>229</v>
-      </c>
-      <c r="B101" t="s">
-        <v>219</v>
-      </c>
-      <c r="C101" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" ht="14.25">
-      <c r="A102" t="s">
-        <v>233</v>
-      </c>
-      <c r="B102" t="s">
-        <v>61</v>
-      </c>
-      <c r="C102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" ht="14.25">
-      <c r="A103" t="s">
-        <v>236</v>
-      </c>
-      <c r="B103" t="s">
-        <v>61</v>
-      </c>
-      <c r="C103" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" ht="14.25">
-      <c r="A104" t="s">
-        <v>240</v>
-      </c>
-      <c r="B104" t="s">
-        <v>150</v>
-      </c>
-      <c r="C104" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" ht="14.25">
-      <c r="A105" t="s">
-        <v>242</v>
-      </c>
-      <c r="B105" t="s">
-        <v>150</v>
-      </c>
-      <c r="C105" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" ht="14.25">
-      <c r="A106" t="s">
-        <v>246</v>
-      </c>
-      <c r="B106" t="s">
-        <v>219</v>
-      </c>
-      <c r="C106" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" ht="14.25"/>
-    <row r="108" ht="14.25"/>
-    <row r="109" ht="14.25"/>
-    <row r="110" ht="14.25"/>
-    <row r="111" ht="14.25"/>
-    <row r="112" ht="14.25"/>
-    <row r="113" ht="14.25"/>
-    <row r="114" ht="14.25"/>
+    <row r="75" ht="14.25"/>
+    <row r="76" ht="14.25"/>
+    <row r="77" ht="14.25"/>
+    <row r="78" ht="14.25"/>
+    <row r="79" ht="14.25"/>
+    <row r="80" ht="14.25"/>
+    <row r="81" ht="14.25"/>
+    <row r="82" ht="14.25"/>
   </sheetData>
-  <sortState ref="A59:C104">
-    <sortCondition ref="A59:A104"/>
+  <sortState ref="A27:C72">
+    <sortCondition ref="A27:A72"/>
   </sortState>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/app/config/tables/MADTRIAL_FU_PHONE/Forms/MADTRIAL_FU_PHONE/MADTRIAL_FU_PHONE.xlsx
+++ b/app/config/tables/MADTRIAL_FU_PHONE/Forms/MADTRIAL_FU_PHONE/MADTRIAL_FU_PHONE.xlsx
@@ -1,9 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MADtrials2\MADtrial\app\config\tables\MADTRIAL_FU_PHONE\Forms\MADTRIAL_FU_PHONE\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B6D433-15AB-4D90-A8D3-DC3640758797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -16,11 +23,24 @@
     <sheet name="model" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="411">
   <si>
     <t>setting_name</t>
   </si>
@@ -112,7 +132,7 @@
     <t>adate</t>
   </si>
   <si>
-    <t xml:space="preserve">Save only mm.dd.yyyy with support for ?? at all positions</t>
+    <t>Save only mm.dd.yyyy with support for ?? at all positions</t>
   </si>
   <si>
     <t>calculation_name</t>
@@ -133,13 +153,13 @@
     <t>MADTRIAL_FU_PHONE</t>
   </si>
   <si>
-    <t xml:space="preserve">begin screen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">end screen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data da ligação</t>
+    <t>begin screen</t>
+  </si>
+  <si>
+    <t>end screen</t>
+  </si>
+  <si>
+    <t>Data da ligação</t>
   </si>
   <si>
     <t>Assistente</t>
@@ -154,10 +174,10 @@
     <t>cham</t>
   </si>
   <si>
-    <t xml:space="preserve">Seguimento realizado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sem rede</t>
+    <t>Seguimento realizado</t>
+  </si>
+  <si>
+    <t>Sem rede</t>
   </si>
   <si>
     <t>integer</t>
@@ -172,7 +192,7 @@
     <t>Outro</t>
   </si>
   <si>
-    <t xml:space="preserve">Ninguem para fornecer informaçeos</t>
+    <t>Ninguem para fornecer informaçeos</t>
   </si>
   <si>
     <t>sim/não</t>
@@ -199,7 +219,7 @@
     <t>VACTIPO</t>
   </si>
   <si>
-    <t xml:space="preserve">Qual vacinas?</t>
+    <t>Qual vacinas?</t>
   </si>
   <si>
     <t>BCG</t>
@@ -223,7 +243,7 @@
     <t>VACOUTRO</t>
   </si>
   <si>
-    <t xml:space="preserve">A criança foi internada no hospital desde que foi vacinada contra sarampo em Simão Mendes?</t>
+    <t>A criança foi internada no hospital desde que foi vacinada contra sarampo em Simão Mendes?</t>
   </si>
   <si>
     <t xml:space="preserve">adate </t>
@@ -235,13 +255,13 @@
     <t>if</t>
   </si>
   <si>
-    <t xml:space="preserve">end if</t>
+    <t>end if</t>
   </si>
   <si>
     <t>HOSPCODE1</t>
   </si>
   <si>
-    <t xml:space="preserve">Local do primeiro Internamento</t>
+    <t>Local do primeiro Internamento</t>
   </si>
   <si>
     <t>HOSPCAUSA1</t>
@@ -265,7 +285,7 @@
     <t>HOSPCODE2</t>
   </si>
   <si>
-    <t xml:space="preserve">A criança esta ainda internada</t>
+    <t>A criança esta ainda internada</t>
   </si>
   <si>
     <t>HOSPI3</t>
@@ -277,7 +297,7 @@
     <t>HOSPDATA3</t>
   </si>
   <si>
-    <t xml:space="preserve">Local do terceiro Internamento</t>
+    <t>Local do terceiro Internamento</t>
   </si>
   <si>
     <t>HOSPCODE3</t>
@@ -334,13 +354,13 @@
     <t>Pai</t>
   </si>
   <si>
-    <t xml:space="preserve">Other caretaker</t>
+    <t>Other caretaker</t>
   </si>
   <si>
     <t>Tutor</t>
   </si>
   <si>
-    <t xml:space="preserve">No one to provide information</t>
+    <t>No one to provide information</t>
   </si>
   <si>
     <t>dodns</t>
@@ -349,10 +369,10 @@
     <t>ns</t>
   </si>
   <si>
-    <t xml:space="preserve">Don't know</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não Sabe</t>
+    <t>Don't know</t>
+  </si>
+  <si>
+    <t>Não Sabe</t>
   </si>
   <si>
     <t>DOB</t>
@@ -361,16 +381,16 @@
     <t>"D:NS,M:NS,Y:NS"</t>
   </si>
   <si>
-    <t xml:space="preserve">Idade - ano(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age - month(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idade - mes(es)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('dodns') != null</t>
+    <t>Idade - ano(s)</t>
+  </si>
+  <si>
+    <t>Age - month(s)</t>
+  </si>
+  <si>
+    <t>Idade - mes(es)</t>
+  </si>
+  <si>
+    <t>data('dodns') != null</t>
   </si>
   <si>
     <t>DODANO</t>
@@ -382,7 +402,7 @@
     <t>data('DOD')=="D:NS,M:NS,Y:NS"</t>
   </si>
   <si>
-    <t xml:space="preserve">data('VACHIS') == '1'</t>
+    <t>data('VACHIS') == '1'</t>
   </si>
   <si>
     <t>data('HOSPI')=="1"</t>
@@ -397,28 +417,28 @@
     <t>vezes</t>
   </si>
   <si>
-    <t xml:space="preserve">More than 3 times</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('HOSPIVEZ') &gt; 0</t>
+    <t>More than 3 times</t>
+  </si>
+  <si>
+    <t>data('HOSPIVEZ') &gt; 0</t>
   </si>
   <si>
     <t>hospalta</t>
   </si>
   <si>
-    <t xml:space="preserve">The child still admitted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('HOSPIVEZ') == '33'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('HOSPIVEZ') == '33' &amp;&amp; data('HOSPI2')=="1"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('HOSPI3')=="1" || data('HOSPIVEZ') == '3' || data('HOSPIVEZ') == '77'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('HOSPI2')=="1" || data('HOSPIVEZ') == '3' || data('HOSPIVEZ') == '2' || data('HOSPIVEZ') == '77'</t>
+    <t>The child still admitted</t>
+  </si>
+  <si>
+    <t>data('HOSPIVEZ') == '33'</t>
+  </si>
+  <si>
+    <t>data('HOSPIVEZ') == '33' &amp;&amp; data('HOSPI2')=="1"</t>
+  </si>
+  <si>
+    <t>data('HOSPI3')=="1" || data('HOSPIVEZ') == '3' || data('HOSPIVEZ') == '77'</t>
+  </si>
+  <si>
+    <t>data('HOSPI2')=="1" || data('HOSPIVEZ') == '3' || data('HOSPIVEZ') == '2' || data('HOSPIVEZ') == '77'</t>
   </si>
   <si>
     <t>Sim</t>
@@ -427,10 +447,10 @@
     <t>Não</t>
   </si>
   <si>
-    <t xml:space="preserve">Não sabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('PODEAUT') == '1'</t>
+    <t>Não sabe</t>
+  </si>
+  <si>
+    <t>data('PODEAUT') == '1'</t>
   </si>
   <si>
     <t>select_one_dropdown</t>
@@ -463,7 +483,7 @@
     <t>Amarelo</t>
   </si>
   <si>
-    <t xml:space="preserve">Yellow fever</t>
+    <t>Yellow fever</t>
   </si>
   <si>
     <t>Ou</t>
@@ -472,40 +492,40 @@
     <t>Other</t>
   </si>
   <si>
-    <t xml:space="preserve">Date of call</t>
+    <t>Date of call</t>
   </si>
   <si>
     <t>Assistant</t>
   </si>
   <si>
-    <t xml:space="preserve">Is the child still alive?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Has the child received other vaccines since being vaccinated at Simão Mendes?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What vaccines?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other Vaccine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How many times?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cause of first admission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length of first internment in days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Has the child been hospitalized more than once?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Has the child been admitted to hospital more than twice?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">We can visit you to ask more questions about your child's death.</t>
+    <t>Is the child still alive?</t>
+  </si>
+  <si>
+    <t>Has the child received other vaccines since being vaccinated at Simão Mendes?</t>
+  </si>
+  <si>
+    <t>What vaccines?</t>
+  </si>
+  <si>
+    <t>Other Vaccine</t>
+  </si>
+  <si>
+    <t>How many times?</t>
+  </si>
+  <si>
+    <t>Cause of first admission</t>
+  </si>
+  <si>
+    <t>Length of first internment in days</t>
+  </si>
+  <si>
+    <t>Has the child been hospitalized more than once?</t>
+  </si>
+  <si>
+    <t>Has the child been admitted to hospital more than twice?</t>
+  </si>
+  <si>
+    <t>We can visit you to ask more questions about your child's death.</t>
   </si>
   <si>
     <t>constraint</t>
@@ -523,7 +543,7 @@
     <t>display.hint.text</t>
   </si>
   <si>
-    <t xml:space="preserve">If you cannot get information on the first call, call each number three times</t>
+    <t>If you cannot get information on the first call, call each number three times</t>
   </si>
   <si>
     <t>START</t>
@@ -535,22 +555,22 @@
     <t>Informant</t>
   </si>
   <si>
-    <t xml:space="preserve">Data do falecimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date of death</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age year(s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data do primeiro internamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date of first admission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location of first admission</t>
+    <t>Data do falecimento</t>
+  </si>
+  <si>
+    <t>Date of death</t>
+  </si>
+  <si>
+    <t>Age year(s)</t>
+  </si>
+  <si>
+    <t>Data do primeiro internamento</t>
+  </si>
+  <si>
+    <t>Date of first admission</t>
+  </si>
+  <si>
+    <t>Location of first admission</t>
   </si>
   <si>
     <t>reg_csv</t>
@@ -559,25 +579,25 @@
     <t>hc_csv</t>
   </si>
   <si>
-    <t xml:space="preserve">Health center / hospital: &lt;b&gt;{{data.HOSPCODE1}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centro de saúde / hospital: &lt;b&gt;{{data.HOSPCODE1}}&lt;/b&gt;</t>
+    <t>Health center / hospital: &lt;b&gt;{{data.HOSPCODE1}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Centro de saúde / hospital: &lt;b&gt;{{data.HOSPCODE1}}&lt;/b&gt;</t>
   </si>
   <si>
     <t>reghosp1</t>
   </si>
   <si>
-    <t xml:space="preserve">Region: &lt;b&gt;{{data.reghosp1}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Região: &lt;b&gt;{{data.reghosp1}}&lt;/b&gt;</t>
+    <t>Region: &lt;b&gt;{{data.reghosp1}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Região: &lt;b&gt;{{data.reghosp1}}&lt;/b&gt;</t>
   </si>
   <si>
     <t>hospcode1ns</t>
   </si>
   <si>
-    <t xml:space="preserve">data('hospcode1ns') != null</t>
+    <t>data('hospcode1ns') != null</t>
   </si>
   <si>
     <t>data('hospcode1ns')</t>
@@ -586,16 +606,16 @@
     <t>choice_filter</t>
   </si>
   <si>
-    <t xml:space="preserve">choice_item.reg === data('reghosp1')</t>
+    <t>choice_item.reg === data('reghosp1')</t>
   </si>
   <si>
     <t>dontknowhosp</t>
   </si>
   <si>
-    <t xml:space="preserve">Other place</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outro lugar</t>
+    <t>Other place</t>
+  </si>
+  <si>
+    <t>Outro lugar</t>
   </si>
   <si>
     <t>query_name</t>
@@ -616,7 +636,7 @@
     <t>"HEALTHCENTRES.csv"</t>
   </si>
   <si>
-    <t xml:space="preserve">_.chain(context)
+    <t>_.chain(context)
 .uniq(function(x) {
 return x.reg
 })
@@ -627,112 +647,112 @@
 }).value()</t>
   </si>
   <si>
-    <t xml:space="preserve">_.map(context, function(place){place.data_value = place.cscode;
+    <t>_.map(context, function(place){place.data_value = place.cscode;
 place.display = {title: {text: place.csname} };
 return place;
 })</t>
   </si>
   <si>
-    <t xml:space="preserve">Date of second admission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location of second admission</t>
+    <t>Date of second admission</t>
+  </si>
+  <si>
+    <t>Location of second admission</t>
   </si>
   <si>
     <t>reghosp2</t>
   </si>
   <si>
-    <t xml:space="preserve">Region: &lt;b&gt;{{data.reghosp2}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Região: &lt;b&gt;{{data.reghosp2}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health center / hospital: &lt;b&gt;{{data.HOSPCODE2}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centro de saúde / hospital: &lt;b&gt;{{data.HOSPCODE2}}&lt;/b&gt;</t>
+    <t>Region: &lt;b&gt;{{data.reghosp2}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Região: &lt;b&gt;{{data.reghosp2}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Health center / hospital: &lt;b&gt;{{data.HOSPCODE2}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Centro de saúde / hospital: &lt;b&gt;{{data.HOSPCODE2}}&lt;/b&gt;</t>
   </si>
   <si>
     <t>hospcode2ns</t>
   </si>
   <si>
-    <t xml:space="preserve">data('hospcode2ns') != null</t>
+    <t>data('hospcode2ns') != null</t>
   </si>
   <si>
     <t>data('hospcode2ns')</t>
   </si>
   <si>
-    <t xml:space="preserve">choice_item.reg === data('reghosp2')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Causa do primeiro internamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Causa do segundo internamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Local do segundo internamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data do segundo internamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duração do primeiro internamento em dias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length of second admission in days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duração do segundo internamento em dias</t>
+    <t>choice_item.reg === data('reghosp2')</t>
+  </si>
+  <si>
+    <t>Causa do primeiro internamento</t>
+  </si>
+  <si>
+    <t>Causa do segundo internamento</t>
+  </si>
+  <si>
+    <t>Local do segundo internamento</t>
+  </si>
+  <si>
+    <t>Data do segundo internamento</t>
+  </si>
+  <si>
+    <t>Duração do primeiro internamento em dias</t>
+  </si>
+  <si>
+    <t>Length of second admission in days</t>
+  </si>
+  <si>
+    <t>Duração do segundo internamento em dias</t>
   </si>
   <si>
     <t>reghosp3</t>
   </si>
   <si>
-    <t xml:space="preserve">Region: &lt;b&gt;{{data.reghosp3}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Região: &lt;b&gt;{{data.reghosp3}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health center / hospital: &lt;b&gt;{{data.HOSPCODE3}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centro de saúde / hospital: &lt;b&gt;{{data.HOSPCODE3}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choice_item.reg === data('reghosp3')</t>
+    <t>Region: &lt;b&gt;{{data.reghosp3}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Região: &lt;b&gt;{{data.reghosp3}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Health center / hospital: &lt;b&gt;{{data.HOSPCODE3}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Centro de saúde / hospital: &lt;b&gt;{{data.HOSPCODE3}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>choice_item.reg === data('reghosp3')</t>
   </si>
   <si>
     <t>hospcode3ns</t>
   </si>
   <si>
-    <t xml:space="preserve">data('hospcode3ns') != null</t>
+    <t>data('hospcode3ns') != null</t>
   </si>
   <si>
     <t>data('hospcode3ns')</t>
   </si>
   <si>
-    <t xml:space="preserve">Data do terceiro internamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Causa do terceiro internamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duração do terceiro internamento em dias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cause of third admission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length of third internment in days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date of third admission</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location of third admission</t>
+    <t>Data do terceiro internamento</t>
+  </si>
+  <si>
+    <t>Causa do terceiro internamento</t>
+  </si>
+  <si>
+    <t>Duração do terceiro internamento em dias</t>
+  </si>
+  <si>
+    <t>Cause of third admission</t>
+  </si>
+  <si>
+    <t>Length of third internment in days</t>
+  </si>
+  <si>
+    <t>Date of third admission</t>
+  </si>
+  <si>
+    <t>Location of third admission</t>
   </si>
   <si>
     <t>Yes</t>
@@ -741,25 +761,25 @@
     <t>No</t>
   </si>
   <si>
-    <t xml:space="preserve">No network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incorrect Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doesn't answer the phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Follow up possible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mais de 3 vezes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name of morança</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome da morança</t>
+    <t>No network</t>
+  </si>
+  <si>
+    <t>Incorrect Number</t>
+  </si>
+  <si>
+    <t>Doesn't answer the phone</t>
+  </si>
+  <si>
+    <t>Follow up possible</t>
+  </si>
+  <si>
+    <t>Mais de 3 vezes</t>
+  </si>
+  <si>
+    <t>Name of morança</t>
+  </si>
+  <si>
+    <t>Nome da morança</t>
   </si>
   <si>
     <t>Oio</t>
@@ -786,19 +806,19 @@
     <t>Bolama</t>
   </si>
   <si>
-    <t xml:space="preserve">The date cannot be in the future:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A data não pode estar no futuro:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('IDADEMES')&lt;13 || data('DOB')!="D:NS,M:NS,Y:NS"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Must be less than 13:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deve ser menor que 13:</t>
+    <t>The date cannot be in the future:</t>
+  </si>
+  <si>
+    <t>A data não pode estar no futuro:</t>
+  </si>
+  <si>
+    <t>data('IDADEMES')&lt;13 || data('DOB')!="D:NS,M:NS,Y:NS"</t>
+  </si>
+  <si>
+    <t>Must be less than 13:</t>
+  </si>
+  <si>
+    <t>Deve ser menor que 13:</t>
   </si>
   <si>
     <t>TELEMOVEL1</t>
@@ -855,25 +875,25 @@
     <t>CHAMADA32</t>
   </si>
   <si>
-    <t xml:space="preserve">data('CHAMADA13') != '1'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CHAMADA23') != '1'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CHAMADA12') != '1'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CHAMADA22') != '1'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CHAMADA11') != '1'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CHAMADA21') != '1'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CHAMADA11') == '1' || data('CHAMADA21') == '1' || data('CHAMADA31') == '1' || data('CHAMADA12') == '1' || data('CHAMADA22') == '1' || data('CHAMADA32') == '1' ||data('CHAMADA13') == '1' || data('CHAMADA23') == '1' || data('CHAMADA33') == '1'</t>
+    <t>data('CHAMADA13') != '1'</t>
+  </si>
+  <si>
+    <t>data('CHAMADA23') != '1'</t>
+  </si>
+  <si>
+    <t>data('CHAMADA12') != '1'</t>
+  </si>
+  <si>
+    <t>data('CHAMADA22') != '1'</t>
+  </si>
+  <si>
+    <t>data('CHAMADA11') != '1'</t>
+  </si>
+  <si>
+    <t>data('CHAMADA21') != '1'</t>
+  </si>
+  <si>
+    <t>data('CHAMADA11') == '1' || data('CHAMADA21') == '1' || data('CHAMADA31') == '1' || data('CHAMADA12') == '1' || data('CHAMADA22') == '1' || data('CHAMADA32') == '1' ||data('CHAMADA13') == '1' || data('CHAMADA23') == '1' || data('CHAMADA33') == '1'</t>
   </si>
   <si>
     <t>call</t>
@@ -900,19 +920,19 @@
     <t>SEX</t>
   </si>
   <si>
-    <t xml:space="preserve">do section FU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1st try</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3rd try</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2nd try</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MADtrial - Follow-up Phone</t>
+    <t>do section FU</t>
+  </si>
+  <si>
+    <t>1st try</t>
+  </si>
+  <si>
+    <t>3rd try</t>
+  </si>
+  <si>
+    <t>2nd try</t>
+  </si>
+  <si>
+    <t>MADtrial - Follow-up Phone</t>
   </si>
   <si>
     <t>IDINC</t>
@@ -924,37 +944,37 @@
     <t>IDADEMES</t>
   </si>
   <si>
-    <t xml:space="preserve">data('CHAMADA11') == '4'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;font color = "red"&gt;As chamadas anteriores informaram que este número está incorreto &lt;/font&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;font color = "red"&gt;Previous calls said this number is incorrect &lt;/font&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CHAMADA21') == '4'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CHAMADA31') == '4'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CHAMADA11') == '4' || data('CHAMADA12') == '4'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CHAMADA31') == '4' || data('CHAMADA32') == '4'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CHAMADA21') == '4' || data('CHAMADA22') == '4'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('chamada1') == '4'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('chamada2') == '4'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('chamada3') == '4'</t>
+    <t>data('CHAMADA11') == '4'</t>
+  </si>
+  <si>
+    <t>&lt;font color = "red"&gt;As chamadas anteriores informaram que este número está incorreto &lt;/font&gt;</t>
+  </si>
+  <si>
+    <t>&lt;font color = "red"&gt;Previous calls said this number is incorrect &lt;/font&gt;</t>
+  </si>
+  <si>
+    <t>data('CHAMADA21') == '4'</t>
+  </si>
+  <si>
+    <t>data('CHAMADA31') == '4'</t>
+  </si>
+  <si>
+    <t>data('CHAMADA11') == '4' || data('CHAMADA12') == '4'</t>
+  </si>
+  <si>
+    <t>data('CHAMADA31') == '4' || data('CHAMADA32') == '4'</t>
+  </si>
+  <si>
+    <t>data('CHAMADA21') == '4' || data('CHAMADA22') == '4'</t>
+  </si>
+  <si>
+    <t>data('chamada1') == '4'</t>
+  </si>
+  <si>
+    <t>data('chamada2') == '4'</t>
+  </si>
+  <si>
+    <t>data('chamada3') == '4'</t>
   </si>
   <si>
     <t>chamada3</t>
@@ -969,49 +989,49 @@
     <t>VPI</t>
   </si>
   <si>
-    <t xml:space="preserve">Name: &lt;b&gt;{{data.NOMECRI}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome: &lt;b&gt;{{data.NOMECRI}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('DOB') == 'D:NS,M:NS,Y:NS'</t>
+    <t>Name: &lt;b&gt;{{data.NOMECRI}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Nome: &lt;b&gt;{{data.NOMECRI}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>data('DOB') == 'D:NS,M:NS,Y:NS'</t>
   </si>
   <si>
     <t>else</t>
   </si>
   <si>
-    <t xml:space="preserve">Birthdate: &lt;b&gt;{{calculates.displayDOB}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data de nascimento: &lt;b&gt;{{calculates.displayDOB}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age: &lt;b&gt;{{data.IDADEANO}}&lt;/b&gt; year(s), &lt;b&gt;{{data.IDADEMES}}&lt;/b&gt; month(s)</t>
+    <t>Birthdate: &lt;b&gt;{{calculates.displayDOB}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Data de nascimento: &lt;b&gt;{{calculates.displayDOB}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Age: &lt;b&gt;{{data.IDADEANO}}&lt;/b&gt; year(s), &lt;b&gt;{{data.IDADEMES}}&lt;/b&gt; month(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Idade: &lt;b&gt;{{data.IDADEANO}}&lt;/b&gt; ano(s), &lt;b&gt;{{data.IDADEMES}}&lt;/b&gt; mes(es) </t>
   </si>
   <si>
-    <t xml:space="preserve">data('SEX') =='1'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sex: &lt;b&gt;Male&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sexo: &lt;b&gt;Masculino&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sex: &lt;b&gt;Female&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sexo: &lt;b&gt;Feminino&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inclusão: &lt;b&gt;{{calculates.displayDATINC}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inclusion: &lt;b&gt;{{calculates.displayDATINC}}&lt;/b&gt;</t>
+    <t>data('SEX') =='1'</t>
+  </si>
+  <si>
+    <t>Sex: &lt;b&gt;Male&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Sexo: &lt;b&gt;Masculino&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Sex: &lt;b&gt;Female&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Sexo: &lt;b&gt;Feminino&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Inclusão: &lt;b&gt;{{calculates.displayDATINC}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Inclusion: &lt;b&gt;{{calculates.displayDATINC}}&lt;/b&gt;</t>
   </si>
   <si>
     <t>displayDATINC</t>
@@ -1020,7 +1040,7 @@
     <t>displayDOB</t>
   </si>
   <si>
-    <t xml:space="preserve">Estudo nº: &lt;b&gt;{{data.NUMEST}}&lt;/b&gt;</t>
+    <t>Estudo nº: &lt;b&gt;{{data.NUMEST}}&lt;/b&gt;</t>
   </si>
   <si>
     <t>adate.display(data('DOB'))</t>
@@ -1029,7 +1049,7 @@
     <t>adate.display(data('DATINC'))</t>
   </si>
   <si>
-    <t xml:space="preserve">Study no.: &lt;b&gt;{{data.NUMEST}}&lt;/b&gt;</t>
+    <t>Study no.: &lt;b&gt;{{data.NUMEST}}&lt;/b&gt;</t>
   </si>
   <si>
     <t>display.adate.helperText</t>
@@ -1044,34 +1064,34 @@
     <t>Farim</t>
   </si>
   <si>
-    <t xml:space="preserve">Sao Domingos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name of mother: &lt;b&gt;{{data.NOMEMAE}}&lt;/b&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome da mãe: &lt;b&gt;{{data.NOMEMAE}}&lt;/b&gt;</t>
+    <t>Sao Domingos</t>
+  </si>
+  <si>
+    <t>Name of mother: &lt;b&gt;{{data.NOMEMAE}}&lt;/b&gt;</t>
+  </si>
+  <si>
+    <t>Nome da mãe: &lt;b&gt;{{data.NOMEMAE}}&lt;/b&gt;</t>
   </si>
   <si>
     <t>NOMEMAE</t>
   </si>
   <si>
-    <t xml:space="preserve">data('CHAMADA12') == null &amp;&amp; data('CHAMADA22') == null &amp;&amp; data('CHAMADA32') == null &amp;&amp; data('CHAMADA13') == null &amp;&amp; data('CHAMADA23') == null &amp;&amp; data('CHAMADA33') == null || (data('DATSEGUI3') == data('DATSEGUI1')) || (data('DATSEGUI2') == data('DATSEGUI1'))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(data('CHAMADA12') != null || data('CHAMADA22') != null || data('CHAMADA32') != null) &amp;&amp; data('DATSEGUI2') != null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">((data('CHAMADA11') != null || data('CHAMADA21') != null || data('CHAMADA31') != null) &amp;&amp; data('CHAMADA13') == null &amp;&amp; data('CHAMADA23') == null &amp;&amp; data('CHAMADA33') == null &amp;&amp; data('DATSEGUI2') != data('DATSEGUI1')) ||  (data('DATSEGUI3') == data('DATSEGUI2') &amp;&amp; data('DATSEGUI3') != null)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(data('CHAMADA11') != null || data('CHAMADA21') != null || data('CHAMADA31') != null) &amp;&amp; (data('CHAMADA12') != null || data('CHAMADA22') != null || data('CHAMADA32') != null)  &amp;&amp; data('DATSEGUI2') != data('DATSEGUI3') &amp;&amp; data('DATSEGUI2') != null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(data('CHAMADA11') != null || data('CHAMADA21') != null || data('CHAMADA31') != null) &amp;&amp; data('CHAMADA13') == null &amp;&amp; data('CHAMADA23') == null &amp;&amp; data('CHAMADA33') == null &amp;&amp; data('DATSEGUI1') != null &amp;&amp; data('DATSEGUI3') == null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data('CHAMADA11') == null &amp;&amp; data('CHAMADA21') == null &amp;&amp; data('CHAMADA31') == null &amp;&amp; data('CHAMADA12') == null &amp;&amp; data('CHAMADA22') == null &amp;&amp; data('CHAMADA32') == null &amp;&amp; data('CHAMADA13') == null &amp;&amp; data('CHAMADA23') == null &amp;&amp; data('CHAMADA33') == null</t>
+    <t>data('CHAMADA12') == null &amp;&amp; data('CHAMADA22') == null &amp;&amp; data('CHAMADA32') == null &amp;&amp; data('CHAMADA13') == null &amp;&amp; data('CHAMADA23') == null &amp;&amp; data('CHAMADA33') == null || (data('DATSEGUI3') == data('DATSEGUI1')) || (data('DATSEGUI2') == data('DATSEGUI1'))</t>
+  </si>
+  <si>
+    <t>(data('CHAMADA12') != null || data('CHAMADA22') != null || data('CHAMADA32') != null) &amp;&amp; data('DATSEGUI2') != null</t>
+  </si>
+  <si>
+    <t>((data('CHAMADA11') != null || data('CHAMADA21') != null || data('CHAMADA31') != null) &amp;&amp; data('CHAMADA13') == null &amp;&amp; data('CHAMADA23') == null &amp;&amp; data('CHAMADA33') == null &amp;&amp; data('DATSEGUI2') != data('DATSEGUI1')) ||  (data('DATSEGUI3') == data('DATSEGUI2') &amp;&amp; data('DATSEGUI3') != null)</t>
+  </si>
+  <si>
+    <t>(data('CHAMADA11') != null || data('CHAMADA21') != null || data('CHAMADA31') != null) &amp;&amp; (data('CHAMADA12') != null || data('CHAMADA22') != null || data('CHAMADA32') != null)  &amp;&amp; data('DATSEGUI2') != data('DATSEGUI3') &amp;&amp; data('DATSEGUI2') != null</t>
+  </si>
+  <si>
+    <t>(data('CHAMADA11') != null || data('CHAMADA21') != null || data('CHAMADA31') != null) &amp;&amp; data('CHAMADA13') == null &amp;&amp; data('CHAMADA23') == null &amp;&amp; data('CHAMADA33') == null &amp;&amp; data('DATSEGUI1') != null &amp;&amp; data('DATSEGUI3') == null</t>
+  </si>
+  <si>
+    <t>data('CHAMADA11') == null &amp;&amp; data('CHAMADA21') == null &amp;&amp; data('CHAMADA31') == null &amp;&amp; data('CHAMADA12') == null &amp;&amp; data('CHAMADA22') == null &amp;&amp; data('CHAMADA32') == null &amp;&amp; data('CHAMADA13') == null &amp;&amp; data('CHAMADA23') == null &amp;&amp; data('CHAMADA33') == null</t>
   </si>
   <si>
     <t>data('DATSEGUI3')</t>
@@ -1086,23 +1106,23 @@
     <t>datsegui</t>
   </si>
   <si>
-    <t xml:space="preserve">adate.diffInDays(data('datsegui'), data('DOD'))&lt;1 || adate.hasUncertainty(data('DOD'))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adate.diffInDays(data('datsegui'), data('HOSPDATA1'))&lt;1 || adate.hasUncertainty(data('HOSPDATA1'))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adate.diffInDays(data('datsegui'), data('HOSPDATA2'))&lt;1 || adate.hasUncertainty(data('HOSPDATA2'))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adate.diffInDays(data('datsegui'), data('HOSPDATA3'))&lt;1 || adate.hasUncertainty(data('HOSPDATA3'))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1st call - number: &lt;b&gt;{{data.TELEMOVEL1}}&lt;/b&gt;
+    <t>adate.diffInDays(data('datsegui'), data('DOD'))&lt;1 || adate.hasUncertainty(data('DOD'))</t>
+  </si>
+  <si>
+    <t>adate.diffInDays(data('datsegui'), data('HOSPDATA1'))&lt;1 || adate.hasUncertainty(data('HOSPDATA1'))</t>
+  </si>
+  <si>
+    <t>adate.diffInDays(data('datsegui'), data('HOSPDATA2'))&lt;1 || adate.hasUncertainty(data('HOSPDATA2'))</t>
+  </si>
+  <si>
+    <t>adate.diffInDays(data('datsegui'), data('HOSPDATA3'))&lt;1 || adate.hasUncertainty(data('HOSPDATA3'))</t>
+  </si>
+  <si>
+    <t>1st call - number: &lt;b&gt;{{data.TELEMOVEL1}}&lt;/b&gt;
 Relation: &lt;b&gt;{{calculates.relation1}}&lt;/b&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">1ª chamada - número: &lt;b&gt;{{data.TELEMOVEL1}}&lt;/b&gt; &lt;br /&gt;
+    <t>1ª chamada - número: &lt;b&gt;{{data.TELEMOVEL1}}&lt;/b&gt; &lt;br /&gt;
 Relação: &lt;b&gt;{{calculates.relationPU1}}&lt;/b&gt;</t>
   </si>
   <si>
@@ -1124,19 +1144,19 @@
     <t>relationPU3</t>
   </si>
   <si>
-    <t xml:space="preserve">2nd call - number: &lt;b&gt;{{data.TELEMOVEL2}}&lt;/b&gt;
+    <t>2nd call - number: &lt;b&gt;{{data.TELEMOVEL2}}&lt;/b&gt;
 Relation: &lt;b&gt;{{calculates.relation2}}&lt;/b&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">2ª chamada - número: &lt;b&gt;{{data.TELEMOVEL2}}&lt;/b&gt; &lt;br /&gt;
+    <t>2ª chamada - número: &lt;b&gt;{{data.TELEMOVEL2}}&lt;/b&gt; &lt;br /&gt;
 Relação: &lt;b&gt;{{calculates.relationPU2}}&lt;/b&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">3ª chamada - número: &lt;b&gt;{{data.TELEMOVEL3}}&lt;/b&gt; &lt;br /&gt;
+    <t>3ª chamada - número: &lt;b&gt;{{data.TELEMOVEL3}}&lt;/b&gt; &lt;br /&gt;
 Relação: &lt;b&gt;{{calculates.relationPU3}}&lt;/b&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">3rd call - number: &lt;b&gt;{{data.TELEMOVEL3}}&lt;/b&gt;
+    <t>3rd call - number: &lt;b&gt;{{data.TELEMOVEL3}}&lt;/b&gt;
 Relation: &lt;b&gt;{{calculates.relation3}}&lt;/b&gt;</t>
   </si>
   <si>
@@ -1167,19 +1187,19 @@
     <t>freebase.relation(data('TELEINF3'),'PU')</t>
   </si>
   <si>
-    <t xml:space="preserve">data('TELEINF2') == '3'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2nd call - number: &lt;b&gt;Don't have&lt;/b&gt;</t>
+    <t>data('TELEINF2') == '3'</t>
+  </si>
+  <si>
+    <t>2nd call - number: &lt;b&gt;Don't have&lt;/b&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">2ª chamada - número: &lt;b&gt;Não tem&lt;/b&gt; </t>
   </si>
   <si>
-    <t xml:space="preserve">data('TELEINF3') == '3'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3rd call - number: &lt;b&gt;Don't have&lt;/b&gt;</t>
+    <t>data('TELEINF3') == '3'</t>
+  </si>
+  <si>
+    <t>3rd call - number: &lt;b&gt;Don't have&lt;/b&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">3ª chamada - número: &lt;b&gt;Não tem&lt;/b&gt; </t>
@@ -1188,43 +1208,43 @@
     <t>Português</t>
   </si>
   <si>
-    <t xml:space="preserve">Se você não consegue obter informação na primeira chamada, liga cada número tres vezes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança ainda está viva?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outra vacina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantas vezes?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança foi internada no hospital mais do que uma vez? ##omit "no hospital" as it could theoretically also be at a health center?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança foi internada no hospital mais do que duas vezes? ##omit "no hospital" as it could theoretically also be at a health center?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Podemos visita-lo para fazer mais perguntas sobre a morte de seu filho/sua filha?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não atende o telemóvel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numero incorreto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Febre amarela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MADtrial - Seguimento Telemovel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A criança recebeu outras vacinas desde que foi vacinada no costa em Simão Mendes?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Has the child been admitted to hospital since being vaccinated against measles at Simão Mendes?</t>
+    <t>Se você não consegue obter informação na primeira chamada, liga cada número tres vezes</t>
+  </si>
+  <si>
+    <t>A criança ainda está viva?</t>
+  </si>
+  <si>
+    <t>Outra vacina</t>
+  </si>
+  <si>
+    <t>Quantas vezes?</t>
+  </si>
+  <si>
+    <t>A criança foi internada no hospital mais do que uma vez? ##omit "no hospital" as it could theoretically also be at a health center?</t>
+  </si>
+  <si>
+    <t>A criança foi internada no hospital mais do que duas vezes? ##omit "no hospital" as it could theoretically also be at a health center?</t>
+  </si>
+  <si>
+    <t>Podemos visita-lo para fazer mais perguntas sobre a morte de seu filho/sua filha?</t>
+  </si>
+  <si>
+    <t>Não atende o telemóvel</t>
+  </si>
+  <si>
+    <t>Numero incorreto</t>
+  </si>
+  <si>
+    <t>Febre amarela</t>
+  </si>
+  <si>
+    <t>MADtrial - Seguimento Telemovel</t>
+  </si>
+  <si>
+    <t>A criança recebeu outras vacinas desde que foi vacinada no costa em Simão Mendes?</t>
+  </si>
+  <si>
+    <t>Has the child been admitted to hospital since being vaccinated against measles at Simão Mendes?</t>
   </si>
   <si>
     <t>Justiniano</t>
@@ -1242,75 +1262,88 @@
     <t>Jailson</t>
   </si>
   <si>
-    <t>Eduardo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 - Suzete removed 16-02-2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augusto da Costa</t>
+    <t>11 - Suzete removed 16-02-2022</t>
+  </si>
+  <si>
+    <t>Augusto da Costa</t>
   </si>
   <si>
     <t>Abrao</t>
+  </si>
+  <si>
+    <t>1 - Eduardo removed 25-07-2025</t>
+  </si>
+  <si>
+    <t>MENA</t>
+  </si>
+  <si>
+    <t>MeningitisA</t>
+  </si>
+  <si>
+    <t>MenA</t>
+  </si>
+  <si>
+    <t>added 2025-07-25</t>
+  </si>
+  <si>
+    <t>MCV2</t>
+  </si>
+  <si>
+    <t>Sarampo2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-406]General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.000000"/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8.000000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color rgb="FF404040"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -1325,7 +1358,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor/>
       </patternFill>
     </fill>
   </fills>
@@ -1342,48 +1374,43 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="4">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0"/>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="164"/>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="1"/>
-    <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="8" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Excel Built-in Normal" xfId="2"/>
+    <cellStyle name="Excel Built-in Normal" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
-    <cellStyle name="Normal 4" xfId="3"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 4" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{908C957F-C4C6-42D0-9062-F34BB2490A0F}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1395,291 +1422,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1942,41 +1686,43 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="13.26953125"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="29"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="27"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="24.7265625"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="28.54296875"/>
+    <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1984,15 +1730,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
-        <v>60120</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>20250725</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2000,7 +1746,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -2014,18 +1760,18 @@
         <v>393</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -2036,95 +1782,96 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="G12:G24">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G12:G24">
     <sortCondition ref="G12"/>
   </sortState>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:L274"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="12.453125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="12.81640625"/>
-    <col customWidth="1" min="3" max="3" width="44.453125"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="22"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="10.453125"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="13.26953125"/>
-    <col bestFit="1" customWidth="1" min="7" max="7" width="44"/>
-    <col customWidth="1" min="8" max="8" width="53.1796875"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="13.1796875"/>
-    <col bestFit="1" customWidth="1" min="10" max="10" width="69"/>
-    <col bestFit="1" customWidth="1" min="11" max="11" width="82.7265625"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.453125" customWidth="1"/>
+    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="44" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="53.1796875" customWidth="1"/>
+    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="69" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="82.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="2" s="14" customFormat="1">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D4" t="s">
         <v>95</v>
       </c>
@@ -2135,7 +1882,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D5" t="s">
         <v>97</v>
       </c>
@@ -2152,7 +1899,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D6" t="s">
         <v>95</v>
       </c>
@@ -2163,7 +1910,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D7" t="s">
         <v>29</v>
       </c>
@@ -2180,33 +1927,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="16" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D12" t="s">
         <v>95</v>
       </c>
@@ -2217,7 +1964,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D13" t="s">
         <v>97</v>
       </c>
@@ -2234,7 +1981,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D14" t="s">
         <v>95</v>
       </c>
@@ -2245,7 +1992,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D15" t="s">
         <v>29</v>
       </c>
@@ -2262,33 +2009,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="18" s="14" customFormat="1">
-      <c r="A18" s="17" t="s">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D20" t="s">
         <v>95</v>
       </c>
@@ -2299,7 +2046,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
         <v>97</v>
       </c>
@@ -2316,7 +2063,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D22" t="s">
         <v>95</v>
       </c>
@@ -2327,7 +2074,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D23" t="s">
         <v>29</v>
       </c>
@@ -2344,69 +2091,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="26" s="14" customFormat="1">
-      <c r="A26" s="15" t="s">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
+    <row r="28" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D28" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" t="s">
         <v>43</v>
       </c>
       <c r="F28" t="s">
         <v>261</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H28" s="4" t="s">
         <v>356</v>
       </c>
       <c r="J28" t="s">
         <v>167</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="K28" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>70</v>
       </c>
       <c r="C29" t="s">
         <v>302</v>
       </c>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30">
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D30" t="s">
         <v>91</v>
       </c>
-      <c r="E30" s="4"/>
       <c r="G30" t="s">
         <v>299</v>
       </c>
@@ -2414,11 +2159,10 @@
         <v>298</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D31" t="s">
         <v>95</v>
       </c>
-      <c r="E31" s="4"/>
       <c r="F31" t="s">
         <v>261</v>
       </c>
@@ -2426,17 +2170,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>71</v>
       </c>
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33">
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D33" t="s">
         <v>91</v>
       </c>
-      <c r="E33" s="4"/>
       <c r="G33" t="s">
         <v>312</v>
       </c>
@@ -2444,7 +2186,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>70</v>
       </c>
@@ -2452,7 +2194,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D35" t="s">
         <v>91</v>
       </c>
@@ -2463,12 +2205,12 @@
         <v>322</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D37" t="s">
         <v>91</v>
       </c>
@@ -2479,12 +2221,12 @@
         <v>324</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>70</v>
       </c>
@@ -2492,7 +2234,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D40" t="s">
         <v>91</v>
       </c>
@@ -2503,12 +2245,12 @@
         <v>319</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D42" t="s">
         <v>91</v>
       </c>
@@ -2519,16 +2261,15 @@
         <v>317</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D44" t="s">
         <v>91</v>
       </c>
-      <c r="E44" s="4"/>
       <c r="G44" t="s">
         <v>326</v>
       </c>
@@ -2536,7 +2277,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D45" t="s">
         <v>91</v>
       </c>
@@ -2547,7 +2288,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D46" t="s">
         <v>91</v>
       </c>
@@ -2558,7 +2299,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D47" t="s">
         <v>95</v>
       </c>
@@ -2569,27 +2310,27 @@
         <v>347</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>38</v>
       </c>
-      <c r="G48" s="11"/>
-    </row>
-    <row r="49">
+      <c r="G48" s="7"/>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>70</v>
       </c>
       <c r="C49" t="s">
         <v>274</v>
       </c>
-      <c r="G49" s="11"/>
-    </row>
-    <row r="50">
+      <c r="G49" s="7"/>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>70</v>
       </c>
@@ -2597,7 +2338,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D52" t="s">
         <v>91</v>
       </c>
@@ -2608,7 +2349,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D53" t="s">
         <v>95</v>
       </c>
@@ -2619,12 +2360,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="55" ht="29">
+    <row r="55" spans="2:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D55" t="s">
         <v>42</v>
       </c>
@@ -2634,33 +2375,31 @@
       <c r="F55" t="s">
         <v>268</v>
       </c>
-      <c r="G55" s="7" t="s">
+      <c r="G55" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="H55" s="7" t="s">
+      <c r="H55" s="4" t="s">
         <v>364</v>
       </c>
       <c r="J55" t="s">
         <v>167</v>
       </c>
-      <c r="K55" s="2" t="s">
+      <c r="K55" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
         <v>70</v>
       </c>
       <c r="C56" t="s">
         <v>304</v>
       </c>
-      <c r="E56" s="4"/>
-    </row>
-    <row r="57">
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D57" t="s">
         <v>91</v>
       </c>
-      <c r="E57" s="4"/>
       <c r="G57" t="s">
         <v>299</v>
       </c>
@@ -2668,11 +2407,10 @@
         <v>298</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D58" t="s">
         <v>95</v>
       </c>
-      <c r="E58" s="4"/>
       <c r="F58" t="s">
         <v>268</v>
       </c>
@@ -2680,17 +2418,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
         <v>71</v>
       </c>
-      <c r="E59" s="4"/>
-    </row>
-    <row r="60">
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D60" t="s">
         <v>91</v>
       </c>
-      <c r="E60" s="4"/>
       <c r="G60" t="s">
         <v>312</v>
       </c>
@@ -2698,7 +2434,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
         <v>70</v>
       </c>
@@ -2706,7 +2442,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D62" t="s">
         <v>91</v>
       </c>
@@ -2717,12 +2453,12 @@
         <v>322</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D64" t="s">
         <v>91</v>
       </c>
@@ -2733,12 +2469,12 @@
         <v>324</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>70</v>
       </c>
@@ -2746,7 +2482,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D67" t="s">
         <v>91</v>
       </c>
@@ -2757,12 +2493,12 @@
         <v>319</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D69" t="s">
         <v>91</v>
       </c>
@@ -2773,16 +2509,15 @@
         <v>317</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D71" t="s">
         <v>91</v>
       </c>
-      <c r="E71" s="4"/>
       <c r="G71" t="s">
         <v>326</v>
       </c>
@@ -2790,7 +2525,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D72" t="s">
         <v>91</v>
       </c>
@@ -2801,7 +2536,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D73" t="s">
         <v>91</v>
       </c>
@@ -2812,7 +2547,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D74" t="s">
         <v>95</v>
       </c>
@@ -2823,17 +2558,17 @@
         <v>347</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>70</v>
       </c>
@@ -2841,12 +2576,12 @@
         <v>275</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>70</v>
       </c>
@@ -2854,7 +2589,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D80" t="s">
         <v>91</v>
       </c>
@@ -2865,7 +2600,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D81" t="s">
         <v>95</v>
       </c>
@@ -2876,12 +2611,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="83" ht="29">
+    <row r="83" spans="2:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D83" t="s">
         <v>42</v>
       </c>
@@ -2891,33 +2626,31 @@
       <c r="F83" t="s">
         <v>269</v>
       </c>
-      <c r="G83" s="7" t="s">
+      <c r="G83" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="H83" s="7" t="s">
+      <c r="H83" s="4" t="s">
         <v>365</v>
       </c>
       <c r="J83" t="s">
         <v>167</v>
       </c>
-      <c r="K83" s="2" t="s">
+      <c r="K83" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>70</v>
       </c>
       <c r="C84" t="s">
         <v>303</v>
       </c>
-      <c r="E84" s="4"/>
-    </row>
-    <row r="85">
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D85" t="s">
         <v>91</v>
       </c>
-      <c r="E85" s="4"/>
       <c r="G85" t="s">
         <v>299</v>
       </c>
@@ -2925,11 +2658,10 @@
         <v>298</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D86" t="s">
         <v>95</v>
       </c>
-      <c r="E86" s="4"/>
       <c r="F86" t="s">
         <v>269</v>
       </c>
@@ -2937,17 +2669,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>71</v>
       </c>
-      <c r="E87" s="4"/>
-    </row>
-    <row r="88">
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D88" t="s">
         <v>91</v>
       </c>
-      <c r="E88" s="4"/>
       <c r="G88" t="s">
         <v>312</v>
       </c>
@@ -2955,7 +2685,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>70</v>
       </c>
@@ -2963,7 +2693,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D90" t="s">
         <v>91</v>
       </c>
@@ -2974,12 +2704,12 @@
         <v>322</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D92" t="s">
         <v>91</v>
       </c>
@@ -2990,12 +2720,12 @@
         <v>324</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
         <v>70</v>
       </c>
@@ -3003,7 +2733,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D95" t="s">
         <v>91</v>
       </c>
@@ -3014,12 +2744,12 @@
         <v>319</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D97" t="s">
         <v>91</v>
       </c>
@@ -3030,16 +2760,15 @@
         <v>317</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D99" t="s">
         <v>91</v>
       </c>
-      <c r="E99" s="4"/>
       <c r="G99" t="s">
         <v>326</v>
       </c>
@@ -3047,7 +2776,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D100" t="s">
         <v>91</v>
       </c>
@@ -3058,7 +2787,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D101" t="s">
         <v>91</v>
       </c>
@@ -3069,7 +2798,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D102" t="s">
         <v>95</v>
       </c>
@@ -3080,84 +2809,82 @@
         <v>347</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="16" t="s">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A108" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="B108" s="14" t="s">
+      <c r="B108" t="s">
         <v>70</v>
       </c>
-      <c r="C108" s="14" t="s">
+      <c r="C108" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="110" ht="29">
+    <row r="110" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D110" t="s">
         <v>42</v>
       </c>
-      <c r="E110" s="4" t="s">
+      <c r="E110" t="s">
         <v>43</v>
       </c>
       <c r="F110" t="s">
         <v>262</v>
       </c>
-      <c r="G110" s="7" t="s">
+      <c r="G110" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="H110" s="7" t="s">
+      <c r="H110" s="4" t="s">
         <v>356</v>
       </c>
       <c r="J110" t="s">
         <v>167</v>
       </c>
-      <c r="K110" s="2" t="s">
+      <c r="K110" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
         <v>70</v>
       </c>
       <c r="C111" t="s">
         <v>297</v>
       </c>
-      <c r="E111" s="4"/>
-    </row>
-    <row r="112">
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D112" t="s">
         <v>91</v>
       </c>
-      <c r="E112" s="4"/>
       <c r="G112" t="s">
         <v>299</v>
       </c>
@@ -3165,11 +2892,10 @@
         <v>298</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D113" t="s">
         <v>95</v>
       </c>
-      <c r="E113" s="4"/>
       <c r="F113" t="s">
         <v>262</v>
       </c>
@@ -3177,17 +2903,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
         <v>71</v>
       </c>
-      <c r="E114" s="4"/>
-    </row>
-    <row r="115">
+    </row>
+    <row r="115" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D115" t="s">
         <v>91</v>
       </c>
-      <c r="E115" s="4"/>
       <c r="G115" t="s">
         <v>312</v>
       </c>
@@ -3195,7 +2919,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
         <v>70</v>
       </c>
@@ -3203,7 +2927,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D117" t="s">
         <v>91</v>
       </c>
@@ -3214,12 +2938,12 @@
         <v>322</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D119" t="s">
         <v>91</v>
       </c>
@@ -3230,12 +2954,12 @@
         <v>324</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B120" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
         <v>70</v>
       </c>
@@ -3243,7 +2967,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D122" t="s">
         <v>91</v>
       </c>
@@ -3254,12 +2978,12 @@
         <v>319</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D124" t="s">
         <v>91</v>
       </c>
@@ -3270,16 +2994,15 @@
         <v>317</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D126" t="s">
         <v>91</v>
       </c>
-      <c r="E126" s="4"/>
       <c r="G126" t="s">
         <v>326</v>
       </c>
@@ -3287,7 +3010,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D127" t="s">
         <v>91</v>
       </c>
@@ -3298,7 +3021,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D128" t="s">
         <v>91</v>
       </c>
@@ -3309,7 +3032,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D129" t="s">
         <v>95</v>
       </c>
@@ -3320,27 +3043,27 @@
         <v>348</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
         <v>38</v>
       </c>
-      <c r="G130" s="11"/>
-    </row>
-    <row r="131">
+      <c r="G130" s="7"/>
+    </row>
+    <row r="131" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
         <v>70</v>
       </c>
       <c r="C131" t="s">
         <v>276</v>
       </c>
-      <c r="G131" s="11"/>
-    </row>
-    <row r="132">
+      <c r="G131" s="7"/>
+    </row>
+    <row r="132" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
         <v>70</v>
       </c>
@@ -3348,7 +3071,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D134" t="s">
         <v>91</v>
       </c>
@@ -3359,7 +3082,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D135" t="s">
         <v>95</v>
       </c>
@@ -3370,12 +3093,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="137" ht="29">
+    <row r="137" spans="2:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D137" t="s">
         <v>42</v>
       </c>
@@ -3385,33 +3108,31 @@
       <c r="F137" t="s">
         <v>272</v>
       </c>
-      <c r="G137" s="7" t="s">
+      <c r="G137" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="H137" s="7" t="s">
+      <c r="H137" s="4" t="s">
         <v>364</v>
       </c>
       <c r="J137" t="s">
         <v>167</v>
       </c>
-      <c r="K137" s="2" t="s">
+      <c r="K137" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
         <v>70</v>
       </c>
       <c r="C138" t="s">
         <v>300</v>
       </c>
-      <c r="E138" s="4"/>
-    </row>
-    <row r="139">
+    </row>
+    <row r="139" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D139" t="s">
         <v>91</v>
       </c>
-      <c r="E139" s="4"/>
       <c r="G139" t="s">
         <v>299</v>
       </c>
@@ -3419,11 +3140,10 @@
         <v>298</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D140" t="s">
         <v>95</v>
       </c>
-      <c r="E140" s="4"/>
       <c r="F140" t="s">
         <v>272</v>
       </c>
@@ -3431,17 +3151,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
         <v>71</v>
       </c>
-      <c r="E141" s="4"/>
-    </row>
-    <row r="142">
+    </row>
+    <row r="142" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D142" t="s">
         <v>91</v>
       </c>
-      <c r="E142" s="4"/>
       <c r="G142" t="s">
         <v>312</v>
       </c>
@@ -3449,7 +3167,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
         <v>70</v>
       </c>
@@ -3457,7 +3175,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D144" t="s">
         <v>91</v>
       </c>
@@ -3468,12 +3186,12 @@
         <v>322</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D146" t="s">
         <v>91</v>
       </c>
@@ -3484,12 +3202,12 @@
         <v>324</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B147" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B148" t="s">
         <v>70</v>
       </c>
@@ -3497,7 +3215,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D149" t="s">
         <v>91</v>
       </c>
@@ -3508,12 +3226,12 @@
         <v>319</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B150" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D151" t="s">
         <v>91</v>
       </c>
@@ -3524,16 +3242,15 @@
         <v>317</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B152" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D153" t="s">
         <v>91</v>
       </c>
-      <c r="E153" s="4"/>
       <c r="G153" t="s">
         <v>326</v>
       </c>
@@ -3541,7 +3258,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D154" t="s">
         <v>91</v>
       </c>
@@ -3552,7 +3269,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D155" t="s">
         <v>91</v>
       </c>
@@ -3563,7 +3280,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D156" t="s">
         <v>95</v>
       </c>
@@ -3574,17 +3291,17 @@
         <v>348</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B157" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B158" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B159" t="s">
         <v>70</v>
       </c>
@@ -3592,12 +3309,12 @@
         <v>277</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B160" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B161" t="s">
         <v>70</v>
       </c>
@@ -3605,7 +3322,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D162" t="s">
         <v>91</v>
       </c>
@@ -3616,7 +3333,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D163" t="s">
         <v>95</v>
       </c>
@@ -3627,12 +3344,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B164" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="165" ht="29">
+    <row r="165" spans="2:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D165" t="s">
         <v>42</v>
       </c>
@@ -3642,33 +3359,31 @@
       <c r="F165" t="s">
         <v>273</v>
       </c>
-      <c r="G165" s="7" t="s">
+      <c r="G165" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="H165" s="7" t="s">
+      <c r="H165" s="4" t="s">
         <v>365</v>
       </c>
       <c r="J165" t="s">
         <v>167</v>
       </c>
-      <c r="K165" s="2" t="s">
+      <c r="K165" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B166" t="s">
         <v>70</v>
       </c>
       <c r="C166" t="s">
         <v>301</v>
       </c>
-      <c r="E166" s="4"/>
-    </row>
-    <row r="167">
+    </row>
+    <row r="167" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D167" t="s">
         <v>91</v>
       </c>
-      <c r="E167" s="4"/>
       <c r="G167" t="s">
         <v>299</v>
       </c>
@@ -3676,11 +3391,10 @@
         <v>298</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D168" t="s">
         <v>95</v>
       </c>
-      <c r="E168" s="4"/>
       <c r="F168" t="s">
         <v>273</v>
       </c>
@@ -3688,17 +3402,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B169" t="s">
         <v>71</v>
       </c>
-      <c r="E169" s="4"/>
-    </row>
-    <row r="170">
+    </row>
+    <row r="170" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D170" t="s">
         <v>91</v>
       </c>
-      <c r="E170" s="4"/>
       <c r="G170" t="s">
         <v>312</v>
       </c>
@@ -3706,7 +3418,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B171" t="s">
         <v>70</v>
       </c>
@@ -3714,7 +3426,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D172" t="s">
         <v>91</v>
       </c>
@@ -3725,12 +3437,12 @@
         <v>322</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B173" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D174" t="s">
         <v>91</v>
       </c>
@@ -3741,12 +3453,12 @@
         <v>324</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B175" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B176" t="s">
         <v>70</v>
       </c>
@@ -3754,7 +3466,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D177" t="s">
         <v>91</v>
       </c>
@@ -3765,12 +3477,12 @@
         <v>319</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B178" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D179" t="s">
         <v>91</v>
       </c>
@@ -3781,16 +3493,15 @@
         <v>317</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B180" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D181" t="s">
         <v>91</v>
       </c>
-      <c r="E181" s="4"/>
       <c r="G181" t="s">
         <v>326</v>
       </c>
@@ -3798,7 +3509,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D182" t="s">
         <v>91</v>
       </c>
@@ -3809,7 +3520,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D183" t="s">
         <v>91</v>
       </c>
@@ -3820,7 +3531,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D184" t="s">
         <v>95</v>
       </c>
@@ -3831,84 +3542,82 @@
         <v>348</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B185" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B186" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B187" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B188" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B189" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="190" s="14" customFormat="1">
-      <c r="A190" s="17" t="s">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A190" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="B190" s="14" t="s">
+      <c r="B190" t="s">
         <v>70</v>
       </c>
-      <c r="C190" s="14" t="s">
+      <c r="C190" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B191" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="192" ht="29">
+    <row r="192" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D192" t="s">
         <v>42</v>
       </c>
-      <c r="E192" s="4" t="s">
+      <c r="E192" t="s">
         <v>43</v>
       </c>
       <c r="F192" t="s">
         <v>259</v>
       </c>
-      <c r="G192" s="7" t="s">
+      <c r="G192" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="H192" s="7" t="s">
+      <c r="H192" s="4" t="s">
         <v>356</v>
       </c>
       <c r="J192" t="s">
         <v>167</v>
       </c>
-      <c r="K192" s="2" t="s">
+      <c r="K192" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B193" t="s">
         <v>70</v>
       </c>
       <c r="C193" t="s">
         <v>305</v>
       </c>
-      <c r="E193" s="4"/>
-    </row>
-    <row r="194">
+    </row>
+    <row r="194" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D194" t="s">
         <v>91</v>
       </c>
-      <c r="E194" s="4"/>
       <c r="G194" t="s">
         <v>299</v>
       </c>
@@ -3916,11 +3625,10 @@
         <v>298</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D195" t="s">
         <v>95</v>
       </c>
-      <c r="E195" s="4"/>
       <c r="F195" t="s">
         <v>259</v>
       </c>
@@ -3928,17 +3636,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B196" t="s">
         <v>71</v>
       </c>
-      <c r="E196" s="4"/>
-    </row>
-    <row r="197">
+    </row>
+    <row r="197" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D197" t="s">
         <v>91</v>
       </c>
-      <c r="E197" s="4"/>
       <c r="G197" t="s">
         <v>312</v>
       </c>
@@ -3946,7 +3652,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B198" t="s">
         <v>70</v>
       </c>
@@ -3954,7 +3660,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D199" t="s">
         <v>91</v>
       </c>
@@ -3965,12 +3671,12 @@
         <v>322</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B200" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D201" t="s">
         <v>91</v>
       </c>
@@ -3981,12 +3687,12 @@
         <v>324</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B202" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B203" t="s">
         <v>70</v>
       </c>
@@ -3994,7 +3700,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D204" t="s">
         <v>91</v>
       </c>
@@ -4005,12 +3711,12 @@
         <v>319</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B205" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D206" t="s">
         <v>91</v>
       </c>
@@ -4021,16 +3727,15 @@
         <v>317</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B207" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D208" t="s">
         <v>91</v>
       </c>
-      <c r="E208" s="4"/>
       <c r="G208" t="s">
         <v>326</v>
       </c>
@@ -4038,7 +3743,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D209" t="s">
         <v>91</v>
       </c>
@@ -4049,7 +3754,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D210" t="s">
         <v>91</v>
       </c>
@@ -4060,7 +3765,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D211" t="s">
         <v>95</v>
       </c>
@@ -4071,27 +3776,27 @@
         <v>349</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B212" t="s">
         <v>38</v>
       </c>
-      <c r="G212" s="11"/>
-    </row>
-    <row r="213">
+      <c r="G212" s="7"/>
+    </row>
+    <row r="213" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B213" t="s">
         <v>70</v>
       </c>
       <c r="C213" t="s">
         <v>278</v>
       </c>
-      <c r="G213" s="11"/>
-    </row>
-    <row r="214">
+      <c r="G213" s="7"/>
+    </row>
+    <row r="214" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B214" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B215" t="s">
         <v>70</v>
       </c>
@@ -4099,7 +3804,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D216" t="s">
         <v>91</v>
       </c>
@@ -4110,7 +3815,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D217" t="s">
         <v>95</v>
       </c>
@@ -4121,12 +3826,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B218" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="219" ht="29">
+    <row r="219" spans="2:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D219" t="s">
         <v>42</v>
       </c>
@@ -4136,33 +3841,31 @@
       <c r="F219" t="s">
         <v>260</v>
       </c>
-      <c r="G219" s="7" t="s">
+      <c r="G219" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="H219" s="7" t="s">
+      <c r="H219" s="4" t="s">
         <v>364</v>
       </c>
       <c r="J219" t="s">
         <v>167</v>
       </c>
-      <c r="K219" s="2" t="s">
+      <c r="K219" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B220" t="s">
         <v>70</v>
       </c>
       <c r="C220" t="s">
         <v>306</v>
       </c>
-      <c r="E220" s="4"/>
-    </row>
-    <row r="221">
+    </row>
+    <row r="221" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D221" t="s">
         <v>91</v>
       </c>
-      <c r="E221" s="4"/>
       <c r="G221" t="s">
         <v>299</v>
       </c>
@@ -4170,11 +3873,10 @@
         <v>298</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D222" t="s">
         <v>95</v>
       </c>
-      <c r="E222" s="4"/>
       <c r="F222" t="s">
         <v>260</v>
       </c>
@@ -4182,17 +3884,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B223" t="s">
         <v>71</v>
       </c>
-      <c r="E223" s="4"/>
-    </row>
-    <row r="224">
+    </row>
+    <row r="224" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D224" t="s">
         <v>91</v>
       </c>
-      <c r="E224" s="4"/>
       <c r="G224" t="s">
         <v>312</v>
       </c>
@@ -4200,7 +3900,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B225" t="s">
         <v>70</v>
       </c>
@@ -4208,7 +3908,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D226" t="s">
         <v>91</v>
       </c>
@@ -4219,12 +3919,12 @@
         <v>322</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B227" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D228" t="s">
         <v>91</v>
       </c>
@@ -4235,12 +3935,12 @@
         <v>324</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B229" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B230" t="s">
         <v>70</v>
       </c>
@@ -4248,7 +3948,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D231" t="s">
         <v>91</v>
       </c>
@@ -4259,12 +3959,12 @@
         <v>319</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B232" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D233" t="s">
         <v>91</v>
       </c>
@@ -4275,16 +3975,15 @@
         <v>317</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B234" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D235" t="s">
         <v>91</v>
       </c>
-      <c r="E235" s="4"/>
       <c r="G235" t="s">
         <v>326</v>
       </c>
@@ -4292,7 +3991,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D236" t="s">
         <v>91</v>
       </c>
@@ -4303,7 +4002,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D237" t="s">
         <v>91</v>
       </c>
@@ -4314,7 +4013,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D238" t="s">
         <v>95</v>
       </c>
@@ -4325,17 +4024,17 @@
         <v>349</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B239" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B240" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B241" t="s">
         <v>70</v>
       </c>
@@ -4343,12 +4042,12 @@
         <v>279</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B242" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B243" t="s">
         <v>70</v>
       </c>
@@ -4356,7 +4055,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D244" t="s">
         <v>91</v>
       </c>
@@ -4367,7 +4066,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D245" t="s">
         <v>95</v>
       </c>
@@ -4378,12 +4077,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B246" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="247" ht="29">
+    <row r="247" spans="2:11" ht="29" x14ac:dyDescent="0.35">
       <c r="D247" t="s">
         <v>42</v>
       </c>
@@ -4393,33 +4092,31 @@
       <c r="F247" t="s">
         <v>263</v>
       </c>
-      <c r="G247" s="7" t="s">
+      <c r="G247" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="H247" s="7" t="s">
+      <c r="H247" s="4" t="s">
         <v>365</v>
       </c>
       <c r="J247" t="s">
         <v>167</v>
       </c>
-      <c r="K247" s="2" t="s">
+      <c r="K247" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B248" t="s">
         <v>70</v>
       </c>
       <c r="C248" t="s">
         <v>307</v>
       </c>
-      <c r="E248" s="4"/>
-    </row>
-    <row r="249">
+    </row>
+    <row r="249" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D249" t="s">
         <v>91</v>
       </c>
-      <c r="E249" s="4"/>
       <c r="G249" t="s">
         <v>299</v>
       </c>
@@ -4427,11 +4124,10 @@
         <v>298</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D250" t="s">
         <v>95</v>
       </c>
-      <c r="E250" s="4"/>
       <c r="F250" t="s">
         <v>263</v>
       </c>
@@ -4439,17 +4135,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B251" t="s">
         <v>71</v>
       </c>
-      <c r="E251" s="4"/>
-    </row>
-    <row r="252">
+    </row>
+    <row r="252" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D252" t="s">
         <v>91</v>
       </c>
-      <c r="E252" s="4"/>
       <c r="G252" t="s">
         <v>312</v>
       </c>
@@ -4457,7 +4151,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B253" t="s">
         <v>70</v>
       </c>
@@ -4465,7 +4159,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D254" t="s">
         <v>91</v>
       </c>
@@ -4476,12 +4170,12 @@
         <v>322</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B255" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D256" t="s">
         <v>91</v>
       </c>
@@ -4492,12 +4186,12 @@
         <v>324</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B257" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B258" t="s">
         <v>70</v>
       </c>
@@ -4505,7 +4199,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D259" t="s">
         <v>91</v>
       </c>
@@ -4516,12 +4210,12 @@
         <v>319</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B260" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D261" t="s">
         <v>91</v>
       </c>
@@ -4532,16 +4226,15 @@
         <v>317</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B262" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D263" t="s">
         <v>91</v>
       </c>
-      <c r="E263" s="4"/>
       <c r="G263" t="s">
         <v>326</v>
       </c>
@@ -4549,7 +4242,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D264" t="s">
         <v>91</v>
       </c>
@@ -4560,7 +4253,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D265" t="s">
         <v>91</v>
       </c>
@@ -4571,7 +4264,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D266" t="s">
         <v>95</v>
       </c>
@@ -4582,32 +4275,32 @@
         <v>349</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B267" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B268" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B269" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B270" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B271" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B272" t="s">
         <v>70</v>
       </c>
@@ -4615,96 +4308,97 @@
         <v>280</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B273" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B274" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:O104"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="12.453125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="12.26953125"/>
-    <col customWidth="1" min="3" max="3" width="32.81640625"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="22"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="16.7265625"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="13.7265625"/>
-    <col customWidth="1" min="7" max="7" width="45.54296875"/>
-    <col customWidth="1" min="8" max="8" width="35.453125"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" width="19"/>
-    <col customWidth="1" min="10" max="10" width="30.7265625"/>
-    <col bestFit="1" customWidth="1" min="11" max="11" width="37.453125"/>
-    <col bestFit="1" customWidth="1" min="12" max="12" width="30.26953125"/>
-    <col bestFit="1" customWidth="1" min="13" max="13" width="23"/>
-    <col customWidth="1" min="14" max="14" width="27.453125"/>
-    <col bestFit="1" customWidth="1" min="15" max="15" width="31.7265625"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.81640625" customWidth="1"/>
+    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="45.54296875" customWidth="1"/>
+    <col min="8" max="8" width="35.453125" customWidth="1"/>
+    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.7265625" customWidth="1"/>
+    <col min="11" max="11" width="37.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.453125" customWidth="1"/>
+    <col min="15" max="15" width="31.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D3" t="s">
         <v>97</v>
       </c>
@@ -4721,17 +4415,17 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D6" t="s">
         <v>42</v>
       </c>
@@ -4744,11 +4438,11 @@
       <c r="G6" t="s">
         <v>152</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>70</v>
       </c>
@@ -4756,7 +4450,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D8" t="s">
         <v>29</v>
       </c>
@@ -4779,7 +4473,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D9" t="s">
         <v>56</v>
       </c>
@@ -4790,7 +4484,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>70</v>
       </c>
@@ -4798,23 +4492,23 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D11" t="s">
         <v>95</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="8" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>70</v>
       </c>
@@ -4822,7 +4516,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D14" t="s">
         <v>46</v>
       </c>
@@ -4836,7 +4530,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D15" t="s">
         <v>46</v>
       </c>
@@ -4859,27 +4553,27 @@
         <v>255</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D20" t="s">
         <v>42</v>
       </c>
@@ -4892,16 +4586,16 @@
       <c r="G20" t="s">
         <v>153</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>70</v>
       </c>
@@ -4909,12 +4603,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D24" t="s">
         <v>56</v>
       </c>
@@ -4931,7 +4625,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D25" t="s">
         <v>41</v>
       </c>
@@ -4941,26 +4635,26 @@
       <c r="G25" t="s">
         <v>155</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D29" t="s">
         <v>42</v>
       </c>
@@ -4977,7 +4671,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>70</v>
       </c>
@@ -4985,7 +4679,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D31" t="s">
         <v>42</v>
       </c>
@@ -4998,21 +4692,21 @@
       <c r="G31" t="s">
         <v>156</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H31" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>70</v>
       </c>
@@ -5020,13 +4714,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>37</v>
       </c>
-      <c r="H35" s="4"/>
-    </row>
-    <row r="36">
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D36" t="s">
         <v>68</v>
       </c>
@@ -5036,7 +4729,7 @@
       <c r="G36" t="s">
         <v>175</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" t="s">
         <v>174</v>
       </c>
       <c r="J36" t="s">
@@ -5049,18 +4742,18 @@
         <v>252</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D37" t="s">
         <v>91</v>
       </c>
       <c r="G37" t="s">
         <v>176</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H37" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D38" t="s">
         <v>137</v>
       </c>
@@ -5077,7 +4770,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D39" t="s">
         <v>137</v>
       </c>
@@ -5093,11 +4786,11 @@
       <c r="H39" t="s">
         <v>180</v>
       </c>
-      <c r="O39" s="13" t="s">
+      <c r="O39" s="9" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D40" t="s">
         <v>56</v>
       </c>
@@ -5107,18 +4800,18 @@
       <c r="F40" t="s">
         <v>184</v>
       </c>
-      <c r="J40" s="13"/>
-    </row>
-    <row r="41">
+      <c r="J40" s="9"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>70</v>
       </c>
       <c r="C41" t="s">
         <v>185</v>
       </c>
-      <c r="J41" s="13"/>
-    </row>
-    <row r="42">
+      <c r="J41" s="9"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D42" t="s">
         <v>95</v>
       </c>
@@ -5128,27 +4821,25 @@
       <c r="I42" t="s">
         <v>186</v>
       </c>
-      <c r="J42" s="13"/>
-    </row>
-    <row r="43">
+      <c r="J42" s="9"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>71</v>
       </c>
-      <c r="J43" s="13"/>
-    </row>
-    <row r="44">
+      <c r="J43" s="9"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>38</v>
       </c>
-      <c r="H44" s="4"/>
-    </row>
-    <row r="45">
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>37</v>
       </c>
-      <c r="H45" s="4"/>
-    </row>
-    <row r="46">
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D46" t="s">
         <v>41</v>
       </c>
@@ -5158,11 +4849,11 @@
       <c r="G46" t="s">
         <v>157</v>
       </c>
-      <c r="H46" s="4" t="s">
+      <c r="H46" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D47" t="s">
         <v>46</v>
       </c>
@@ -5172,11 +4863,11 @@
       <c r="G47" t="s">
         <v>158</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="H47" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D48" t="s">
         <v>56</v>
       </c>
@@ -5186,29 +4877,26 @@
       <c r="F48" t="s">
         <v>93</v>
       </c>
-      <c r="H48" s="4"/>
-    </row>
-    <row r="49">
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>38</v>
       </c>
-      <c r="H49" s="4"/>
-    </row>
-    <row r="50">
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>70</v>
       </c>
       <c r="C50" t="s">
         <v>129</v>
       </c>
-      <c r="H50" s="4"/>
-    </row>
-    <row r="51">
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D52" t="s">
         <v>42</v>
       </c>
@@ -5221,21 +4909,21 @@
       <c r="G52" t="s">
         <v>159</v>
       </c>
-      <c r="H52" s="2" t="s">
+      <c r="H52" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>70</v>
       </c>
@@ -5243,13 +4931,12 @@
         <v>132</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
         <v>37</v>
       </c>
-      <c r="H56" s="4"/>
-    </row>
-    <row r="57">
+    </row>
+    <row r="57" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D57" t="s">
         <v>68</v>
       </c>
@@ -5272,18 +4959,18 @@
         <v>252</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D58" t="s">
         <v>91</v>
       </c>
       <c r="G58" t="s">
         <v>201</v>
       </c>
-      <c r="H58" s="4" t="s">
+      <c r="H58" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D59" t="s">
         <v>137</v>
       </c>
@@ -5300,7 +4987,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D60" t="s">
         <v>137</v>
       </c>
@@ -5316,11 +5003,11 @@
       <c r="H60" t="s">
         <v>206</v>
       </c>
-      <c r="O60" s="13" t="s">
+      <c r="O60" s="9" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D61" t="s">
         <v>56</v>
       </c>
@@ -5330,18 +5017,18 @@
       <c r="F61" t="s">
         <v>207</v>
       </c>
-      <c r="J61" s="13"/>
-    </row>
-    <row r="62">
+      <c r="J61" s="9"/>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
         <v>70</v>
       </c>
       <c r="C62" t="s">
         <v>208</v>
       </c>
-      <c r="J62" s="13"/>
-    </row>
-    <row r="63">
+      <c r="J62" s="9"/>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D63" t="s">
         <v>95</v>
       </c>
@@ -5351,27 +5038,25 @@
       <c r="I63" t="s">
         <v>209</v>
       </c>
-      <c r="J63" s="13"/>
-    </row>
-    <row r="64">
+      <c r="J63" s="9"/>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
         <v>71</v>
       </c>
-      <c r="J64" s="13"/>
-    </row>
-    <row r="65">
+      <c r="J64" s="9"/>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
         <v>38</v>
       </c>
-      <c r="H65" s="4"/>
-    </row>
-    <row r="66">
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>37</v>
       </c>
-      <c r="H66" s="4"/>
-    </row>
-    <row r="67">
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
       <c r="D67" t="s">
         <v>41</v>
       </c>
@@ -5381,11 +5066,11 @@
       <c r="G67" t="s">
         <v>157</v>
       </c>
-      <c r="H67" s="4" t="s">
+      <c r="H67" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
       <c r="D68" t="s">
         <v>46</v>
       </c>
@@ -5399,7 +5084,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
       <c r="D69" t="s">
         <v>56</v>
       </c>
@@ -5409,20 +5094,18 @@
       <c r="F69" t="s">
         <v>79</v>
       </c>
-      <c r="H69" s="4"/>
-    </row>
-    <row r="70">
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
         <v>38</v>
       </c>
-      <c r="H70" s="4"/>
-    </row>
-    <row r="71">
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
         <v>70</v>
       </c>
@@ -5430,12 +5113,12 @@
         <v>130</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
       <c r="D74" t="s">
         <v>42</v>
       </c>
@@ -5448,21 +5131,21 @@
       <c r="G74" t="s">
         <v>160</v>
       </c>
-      <c r="H74" s="2" t="s">
+      <c r="H74" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>83</v>
       </c>
@@ -5470,13 +5153,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
         <v>37</v>
       </c>
-      <c r="H78" s="4"/>
-    </row>
-    <row r="79">
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.35">
       <c r="D79" t="s">
         <v>68</v>
       </c>
@@ -5486,25 +5168,25 @@
       <c r="G79" t="s">
         <v>232</v>
       </c>
-      <c r="H79" s="4" t="s">
+      <c r="H79" t="s">
         <v>227</v>
       </c>
       <c r="J79" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.35">
       <c r="D80" t="s">
         <v>91</v>
       </c>
       <c r="G80" t="s">
         <v>233</v>
       </c>
-      <c r="H80" s="4" t="s">
+      <c r="H80" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D81" t="s">
         <v>137</v>
       </c>
@@ -5521,7 +5203,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D82" t="s">
         <v>137</v>
       </c>
@@ -5537,11 +5219,11 @@
       <c r="H82" t="s">
         <v>222</v>
       </c>
-      <c r="O82" s="13" t="s">
+      <c r="O82" s="9" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D83" t="s">
         <v>56</v>
       </c>
@@ -5551,18 +5233,18 @@
       <c r="F83" t="s">
         <v>224</v>
       </c>
-      <c r="J83" s="13"/>
-    </row>
-    <row r="84">
+      <c r="J83" s="9"/>
+    </row>
+    <row r="84" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>70</v>
       </c>
       <c r="C84" t="s">
         <v>225</v>
       </c>
-      <c r="J84" s="13"/>
-    </row>
-    <row r="85">
+      <c r="J84" s="9"/>
+    </row>
+    <row r="85" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D85" t="s">
         <v>95</v>
       </c>
@@ -5572,27 +5254,25 @@
       <c r="I85" t="s">
         <v>226</v>
       </c>
-      <c r="J85" s="13"/>
-    </row>
-    <row r="86">
+      <c r="J85" s="9"/>
+    </row>
+    <row r="86" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>71</v>
       </c>
-      <c r="J86" s="13"/>
-    </row>
-    <row r="87">
+      <c r="J86" s="9"/>
+    </row>
+    <row r="87" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>38</v>
       </c>
-      <c r="H87" s="4"/>
-    </row>
-    <row r="88">
+    </row>
+    <row r="88" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>37</v>
       </c>
-      <c r="H88" s="4"/>
-    </row>
-    <row r="89">
+    </row>
+    <row r="89" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D89" t="s">
         <v>41</v>
       </c>
@@ -5602,11 +5282,11 @@
       <c r="G89" t="s">
         <v>230</v>
       </c>
-      <c r="H89" s="4" t="s">
+      <c r="H89" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D90" t="s">
         <v>46</v>
       </c>
@@ -5616,11 +5296,11 @@
       <c r="G90" t="s">
         <v>231</v>
       </c>
-      <c r="H90" s="4" t="s">
+      <c r="H90" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="2:15" x14ac:dyDescent="0.35">
       <c r="D91" t="s">
         <v>56</v>
       </c>
@@ -5630,25 +5310,23 @@
       <c r="F91" t="s">
         <v>89</v>
       </c>
-      <c r="H91" s="4"/>
-    </row>
-    <row r="92">
+    </row>
+    <row r="92" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
         <v>38</v>
       </c>
-      <c r="H92" s="4"/>
-    </row>
-    <row r="93">
+    </row>
+    <row r="93" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
         <v>70</v>
       </c>
@@ -5656,12 +5334,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D97" t="s">
         <v>42</v>
       </c>
@@ -5674,11 +5352,11 @@
       <c r="G97" t="s">
         <v>161</v>
       </c>
-      <c r="H97" s="2" t="s">
+      <c r="H97" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
         <v>70</v>
       </c>
@@ -5686,7 +5364,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D99" t="s">
         <v>137</v>
       </c>
@@ -5703,7 +5381,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D100" t="s">
         <v>41</v>
       </c>
@@ -5717,7 +5395,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D101" t="s">
         <v>41</v>
       </c>
@@ -5731,52 +5409,53 @@
         <v>242</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="16.81640625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="12.1796875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="15.7265625"/>
-    <col customWidth="1" min="4" max="4" width="58"/>
+    <col min="1" max="1" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="2" ht="130.5">
+    <row r="2" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>177</v>
       </c>
@@ -5786,11 +5465,11 @@
       <c r="C2" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="3" ht="58">
+    <row r="3" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>178</v>
       </c>
@@ -5800,40 +5479,41 @@
       <c r="C3" t="s">
         <v>197</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="4" t="s">
         <v>199</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:E146"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="16.54296875"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="13.81640625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="31.453125"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="43"/>
+    <col min="1" max="1" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -5848,22 +5528,22 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="2" t="str">
+      <c r="B3" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>236</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -5874,11 +5554,11 @@
       <c r="C4" t="s">
         <v>238</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -5889,11 +5569,11 @@
       <c r="C5" t="s">
         <v>237</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -5904,11 +5584,11 @@
       <c r="C6" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>99</v>
       </c>
@@ -5923,7 +5603,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>99</v>
       </c>
@@ -5938,7 +5618,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>99</v>
       </c>
@@ -5953,7 +5633,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -5964,11 +5644,11 @@
       <c r="C10" t="s">
         <v>234</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -5979,11 +5659,11 @@
       <c r="C11" t="s">
         <v>235</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -5994,11 +5674,11 @@
       <c r="C12" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>57</v>
       </c>
@@ -6012,7 +5692,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>57</v>
       </c>
@@ -6026,7 +5706,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -6040,7 +5720,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>57</v>
       </c>
@@ -6054,7 +5734,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -6068,7 +5748,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>57</v>
       </c>
@@ -6082,7 +5762,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>57</v>
       </c>
@@ -6096,7 +5776,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -6106,899 +5786,894 @@
       <c r="C20" t="s">
         <v>147</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>57</v>
       </c>
       <c r="B21" t="s">
+        <v>405</v>
+      </c>
+      <c r="C21" t="s">
+        <v>406</v>
+      </c>
+      <c r="D21" t="s">
+        <v>407</v>
+      </c>
+      <c r="E21" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" t="s">
+        <v>409</v>
+      </c>
+      <c r="C22" t="s">
+        <v>409</v>
+      </c>
+      <c r="D22" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" t="s">
         <v>148</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C23" t="s">
         <v>149</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>51</v>
-      </c>
-      <c r="B22" t="str">
-        <f>"1"</f>
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
-        <v>234</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" t="str">
-        <f>"2"</f>
-        <v>2</v>
-      </c>
-      <c r="C23" t="s">
-        <v>235</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="B24" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>401</v>
+        <v>234</v>
       </c>
       <c r="D24" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
-        <v>98</v>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>51</v>
       </c>
       <c r="B25" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
       <c r="C25" t="s">
+        <v>235</v>
+      </c>
+      <c r="D25" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E26" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" t="str">
+        <f>"2"</f>
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
         <v>400</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D27" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>98</v>
       </c>
-      <c r="B26" t="str">
+      <c r="B28" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C28" t="s">
         <v>398</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D28" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>98</v>
       </c>
-      <c r="B27" t="str">
+      <c r="B29" t="str">
         <f>"10"</f>
         <v>10</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C29" t="s">
         <v>397</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D29" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>98</v>
       </c>
-      <c r="B28" t="str">
+      <c r="B30" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
-      <c r="C28" t="s">
-        <v>403</v>
-      </c>
-      <c r="D28" t="s">
-        <v>403</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="C30" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="s">
+      <c r="D30" t="s">
+        <v>402</v>
+      </c>
+      <c r="E30" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>98</v>
       </c>
-      <c r="B29" t="str">
+      <c r="B31" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
-      <c r="C29" t="s">
-        <v>404</v>
-      </c>
-      <c r="D29" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="s">
+      <c r="C31" t="s">
+        <v>403</v>
+      </c>
+      <c r="D31" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>98</v>
       </c>
-      <c r="B30" t="str">
+      <c r="B32" t="str">
         <f>"12"</f>
         <v>12</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C32" t="s">
         <v>396</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D32" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>108</v>
       </c>
-      <c r="B31" t="str">
+      <c r="B33" t="str">
         <f>"99"</f>
         <v>99</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C33" t="s">
         <v>109</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D33" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>124</v>
       </c>
-      <c r="B32" t="str">
+      <c r="B34" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="C32" t="str">
+      <c r="C34" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="D32" t="str">
+      <c r="D34" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>124</v>
       </c>
-      <c r="B33" t="str">
+      <c r="B35" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
-      <c r="C33" t="str">
+      <c r="C35" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
-      <c r="D33" t="str">
+      <c r="D35" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>124</v>
       </c>
-      <c r="B34" t="str">
+      <c r="B36" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
-      <c r="C34" t="str">
+      <c r="C36" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
-      <c r="D34" t="str">
+      <c r="D36" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
-      <c r="B35" t="str">
+      <c r="B37" t="str">
         <f>"77"</f>
         <v>77</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C37" t="s">
         <v>125</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D37" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>124</v>
       </c>
-      <c r="B36" t="str">
+      <c r="B38" t="str">
         <f>"33"</f>
         <v>33</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C38" t="s">
         <v>109</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D38" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>127</v>
       </c>
-      <c r="B37" t="str">
+      <c r="B39" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C39" t="s">
         <v>128</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D39" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>189</v>
       </c>
-      <c r="B38" t="str">
+      <c r="B40" t="str">
         <f>"88888"</f>
         <v>88888</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C40" t="s">
         <v>190</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D40" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>189</v>
       </c>
-      <c r="B39" t="str">
+      <c r="B41" t="str">
         <f>"77777"</f>
         <v>77777</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C41" t="s">
         <v>109</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D41" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>138</v>
       </c>
-      <c r="B40" t="str">
+      <c r="B42" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C42" t="s">
         <v>334</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D42" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>138</v>
       </c>
-      <c r="B41" t="str">
+      <c r="B43" t="str">
         <f>"1"</f>
         <v>1</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C43" t="s">
         <v>243</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D43" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>138</v>
       </c>
-      <c r="B42" t="str">
+      <c r="B44" t="str">
         <f>"4"</f>
         <v>4</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C44" t="s">
         <v>336</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D44" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>138</v>
       </c>
-      <c r="B43" t="str">
+      <c r="B45" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C45" t="s">
         <v>244</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D45" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>138</v>
       </c>
-      <c r="B44" t="str">
+      <c r="B46" t="str">
         <f>"7"</f>
         <v>7</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C46" t="s">
         <v>246</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D46" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>138</v>
       </c>
-      <c r="B45" t="str">
+      <c r="B47" t="str">
         <f>"15"</f>
         <v>15</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C47" t="s">
         <v>337</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D47" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="s">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>138</v>
       </c>
-      <c r="B46" t="str">
+      <c r="B48" t="str">
         <f>"8"</f>
         <v>8</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C48" t="s">
         <v>247</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D48" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="s">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>138</v>
       </c>
-      <c r="B47" t="str">
+      <c r="B49" t="str">
         <f>"5"</f>
         <v>5</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C49" t="s">
         <v>245</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D49" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>138</v>
       </c>
-      <c r="B48" t="str">
+      <c r="B50" t="str">
         <f>"11"</f>
         <v>11</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C50" t="s">
         <v>248</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D50" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="s">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
-      <c r="B49" t="str">
+      <c r="B51" t="str">
         <f>"12"</f>
         <v>12</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C51" t="s">
         <v>249</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D51" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="s">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>138</v>
       </c>
-      <c r="B50" t="str">
+      <c r="B52" t="str">
         <f>"13"</f>
         <v>13</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C52" t="s">
         <v>335</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D52" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>138</v>
       </c>
-      <c r="B51" t="str">
+      <c r="B53" t="str">
         <f>"14"</f>
         <v>14</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C53" t="s">
         <v>250</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D53" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4"/>
-      <c r="D60" s="2"/>
-    </row>
-    <row r="62">
-      <c r="B62" s="8"/>
-    </row>
-    <row r="63">
-      <c r="B63" s="8"/>
-    </row>
-    <row r="64">
-      <c r="B64" s="8"/>
-    </row>
-    <row r="65">
-      <c r="B65" s="8"/>
-    </row>
-    <row r="66">
-      <c r="B66" s="8"/>
-    </row>
-    <row r="67">
-      <c r="B67" s="8"/>
-    </row>
-    <row r="68">
-      <c r="B68" s="8"/>
-    </row>
-    <row r="69">
-      <c r="B69" s="8"/>
-    </row>
-    <row r="70">
-      <c r="B70" s="8"/>
-    </row>
-    <row r="71">
-      <c r="B71" s="8"/>
-    </row>
-    <row r="72">
-      <c r="B72" s="8"/>
-    </row>
-    <row r="73">
-      <c r="B73" s="8"/>
-    </row>
-    <row r="74">
-      <c r="B74" s="8"/>
-    </row>
-    <row r="75">
-      <c r="B75" s="8"/>
-    </row>
-    <row r="76">
-      <c r="B76" s="8"/>
-    </row>
-    <row r="77">
-      <c r="B77" s="8"/>
-    </row>
-    <row r="78">
-      <c r="B78" s="8"/>
-    </row>
-    <row r="79">
-      <c r="B79" s="8"/>
-    </row>
-    <row r="80">
-      <c r="B80" s="8"/>
-    </row>
-    <row r="81">
-      <c r="B81" s="8"/>
-    </row>
-    <row r="82">
-      <c r="B82" s="8"/>
-    </row>
-    <row r="83">
-      <c r="B83" s="8"/>
-    </row>
-    <row r="84">
-      <c r="B84" s="8"/>
-    </row>
-    <row r="85">
-      <c r="B85" s="8"/>
-    </row>
-    <row r="86">
-      <c r="B86" s="8"/>
-    </row>
-    <row r="87">
-      <c r="B87" s="8"/>
-    </row>
-    <row r="88">
-      <c r="B88" s="8"/>
-    </row>
-    <row r="89">
-      <c r="B89" s="8"/>
-    </row>
-    <row r="90">
-      <c r="B90" s="8"/>
-    </row>
-    <row r="91">
-      <c r="B91" s="8"/>
-    </row>
-    <row r="92">
-      <c r="B92" s="8"/>
-    </row>
-    <row r="93">
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
-    </row>
-    <row r="94">
-      <c r="B94" s="8"/>
-      <c r="C94" s="8"/>
-    </row>
-    <row r="95">
-      <c r="B95" s="8"/>
-      <c r="C95" s="8"/>
-    </row>
-    <row r="96">
-      <c r="B96" s="8"/>
-      <c r="C96" s="8"/>
-    </row>
-    <row r="97">
-      <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
-    </row>
-    <row r="98">
-      <c r="B98" s="8"/>
-      <c r="C98" s="8"/>
-    </row>
-    <row r="99">
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
-    </row>
-    <row r="100">
-      <c r="C100" s="8"/>
-    </row>
-    <row r="101">
-      <c r="B101" s="8"/>
-      <c r="C101" s="8"/>
-    </row>
-    <row r="102">
-      <c r="B102" s="8"/>
-      <c r="C102" s="8"/>
-    </row>
-    <row r="103">
-      <c r="B103" s="8"/>
-      <c r="C103" s="8"/>
-    </row>
-    <row r="104">
-      <c r="B104" s="8"/>
-      <c r="C104" s="8"/>
-    </row>
-    <row r="105">
-      <c r="B105" s="8"/>
-      <c r="C105" s="8"/>
-    </row>
-    <row r="106">
-      <c r="B106" s="8"/>
-      <c r="C106" s="8"/>
-    </row>
-    <row r="107">
-      <c r="B107" s="8"/>
-      <c r="C107" s="8"/>
-    </row>
-    <row r="108">
-      <c r="B108" s="8"/>
-      <c r="C108" s="8"/>
-    </row>
-    <row r="109">
-      <c r="B109" s="8"/>
-      <c r="C109" s="8"/>
-    </row>
-    <row r="110">
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
-    </row>
-    <row r="111">
-      <c r="B111" s="8"/>
-      <c r="C111" s="8"/>
-    </row>
-    <row r="112">
-      <c r="B112" s="8"/>
-      <c r="C112" s="8"/>
-    </row>
-    <row r="113">
-      <c r="B113" s="8"/>
-      <c r="C113" s="8"/>
-    </row>
-    <row r="114">
-      <c r="B114" s="8"/>
-      <c r="C114" s="8"/>
-    </row>
-    <row r="115">
-      <c r="B115" s="8"/>
-      <c r="C115" s="8"/>
-    </row>
-    <row r="116">
-      <c r="B116" s="8"/>
-      <c r="C116" s="8"/>
-    </row>
-    <row r="117">
-      <c r="B117" s="8"/>
-      <c r="C117" s="8"/>
-    </row>
-    <row r="118">
-      <c r="B118" s="8"/>
-      <c r="C118" s="8"/>
-    </row>
-    <row r="119">
-      <c r="B119" s="8"/>
-    </row>
-    <row r="120">
-      <c r="B120" s="8"/>
-    </row>
-    <row r="121">
-      <c r="B121" s="8"/>
-    </row>
-    <row r="122">
-      <c r="B122" s="8"/>
-    </row>
-    <row r="123">
-      <c r="B123" s="8"/>
-    </row>
-    <row r="124">
-      <c r="B124" s="8"/>
-    </row>
-    <row r="125">
-      <c r="B125" s="8"/>
-    </row>
-    <row r="127">
-      <c r="B127" s="8"/>
-    </row>
-    <row r="128">
-      <c r="B128" s="8"/>
-    </row>
-    <row r="129">
-      <c r="B129" s="8"/>
-    </row>
-    <row r="130">
-      <c r="B130" s="8"/>
-    </row>
-    <row r="131">
-      <c r="B131" s="8"/>
-    </row>
-    <row r="132">
-      <c r="B132" s="8"/>
-    </row>
-    <row r="133">
-      <c r="B133" s="8"/>
-    </row>
-    <row r="134">
-      <c r="B134" s="8"/>
-    </row>
-    <row r="135">
-      <c r="B135" s="8"/>
-    </row>
-    <row r="136">
-      <c r="B136" s="8"/>
-    </row>
-    <row r="137">
-      <c r="B137" s="8"/>
-    </row>
-    <row r="138">
-      <c r="B138" s="8"/>
-    </row>
-    <row r="139">
-      <c r="B139" s="8"/>
-    </row>
-    <row r="140">
-      <c r="B140" s="8"/>
-    </row>
-    <row r="141">
-      <c r="B141" s="8"/>
-    </row>
-    <row r="142">
-      <c r="B142" s="8"/>
-    </row>
-    <row r="143">
-      <c r="B143" s="8"/>
-    </row>
-    <row r="144">
-      <c r="B144" s="8"/>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B64" s="5"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B65" s="5"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B66" s="5"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B67" s="5"/>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B68" s="5"/>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B69" s="5"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B70" s="5"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B71" s="5"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B72" s="5"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B73" s="5"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B74" s="5"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B75" s="5"/>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B76" s="5"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B77" s="5"/>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B78" s="5"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B79" s="5"/>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B80" s="5"/>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B81" s="5"/>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B82" s="5"/>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B83" s="5"/>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B84" s="5"/>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B85" s="5"/>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B86" s="5"/>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B87" s="5"/>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B88" s="5"/>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B89" s="5"/>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B90" s="5"/>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B91" s="5"/>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B92" s="5"/>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B93" s="5"/>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B94" s="5"/>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B100" s="5"/>
+      <c r="C100" s="5"/>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B101" s="5"/>
+      <c r="C101" s="5"/>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C102" s="5"/>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B103" s="5"/>
+      <c r="C103" s="5"/>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B104" s="5"/>
+      <c r="C104" s="5"/>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B105" s="5"/>
+      <c r="C105" s="5"/>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B106" s="5"/>
+      <c r="C106" s="5"/>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B107" s="5"/>
+      <c r="C107" s="5"/>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B108" s="5"/>
+      <c r="C108" s="5"/>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B109" s="5"/>
+      <c r="C109" s="5"/>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B110" s="5"/>
+      <c r="C110" s="5"/>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B111" s="5"/>
+      <c r="C111" s="5"/>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B112" s="5"/>
+      <c r="C112" s="5"/>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B113" s="5"/>
+      <c r="C113" s="5"/>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B114" s="5"/>
+      <c r="C114" s="5"/>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B115" s="5"/>
+      <c r="C115" s="5"/>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B116" s="5"/>
+      <c r="C116" s="5"/>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B117" s="5"/>
+      <c r="C117" s="5"/>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B118" s="5"/>
+      <c r="C118" s="5"/>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B119" s="5"/>
+      <c r="C119" s="5"/>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B120" s="5"/>
+      <c r="C120" s="5"/>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B121" s="5"/>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B122" s="5"/>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B123" s="5"/>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B124" s="5"/>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B125" s="5"/>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B126" s="5"/>
+    </row>
+    <row r="127" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B127" s="5"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B129" s="5"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B130" s="5"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B131" s="5"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B132" s="5"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B133" s="5"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B134" s="5"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B135" s="5"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B136" s="5"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B137" s="5"/>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B138" s="5"/>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B139" s="5"/>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B140" s="5"/>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B141" s="5"/>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B142" s="5"/>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B143" s="5"/>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B144" s="5"/>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B145" s="5"/>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B146" s="5"/>
     </row>
   </sheetData>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="16.7265625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="40.54296875"/>
+    <col min="1" max="1" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" s="13" customFormat="1">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="9" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="3" s="13" customFormat="1">
-      <c r="A3" s="13" t="s">
+    <row r="3" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="9" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="4" s="13" customFormat="1">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="9" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="5" s="13" customFormat="1">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="9" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="6" s="13" customFormat="1">
-      <c r="A6" s="13" t="s">
+    <row r="6" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="9" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="7" s="13" customFormat="1">
-      <c r="A7" s="13" t="s">
+    <row r="7" spans="1:2" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="9" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>328</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="9" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>327</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="9" t="s">
         <v>331</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="18.81640625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="6"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="12.81640625"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="34.1796875"/>
+    <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -7013,215 +6688,215 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:D77"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col bestFit="1" customWidth="1" min="1" max="1" width="13.7265625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="23.1796875"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="16.7265625"/>
+    <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" s="14" customFormat="1">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>264</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="14" t="b">
+      <c r="C2" t="b">
         <v>0</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="3" s="14" customFormat="1">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>271</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="14" t="b">
+      <c r="C3" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" s="14" customFormat="1">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>267</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="14" t="b">
+      <c r="C4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" s="14" customFormat="1">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>259</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="14" t="b">
+      <c r="C5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" s="14" customFormat="1">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>262</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="14" t="b">
+      <c r="C6" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="14" customFormat="1">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>261</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="14" t="b">
+      <c r="C7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8" s="14" customFormat="1">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>260</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="14" t="b">
+      <c r="C8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" s="14" customFormat="1">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>272</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="14" t="b">
+      <c r="C9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" s="14" customFormat="1">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>268</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="14" t="b">
+      <c r="C10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="14" customFormat="1">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>263</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="14" t="b">
+      <c r="C11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" s="14" customFormat="1">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>273</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="14" t="b">
+      <c r="C12" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" s="14" customFormat="1">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>269</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="14" t="b">
+      <c r="C13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" s="14" customFormat="1">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>265</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="14" t="b">
+      <c r="C14" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" s="14" customFormat="1">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>270</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="14" t="b">
+      <c r="C15" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16" s="14" customFormat="1">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>266</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="14" t="b">
+      <c r="C16" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="17" s="14" customFormat="1">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>168</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="14" t="b">
+      <c r="C17" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="18" s="4" customFormat="1"/>
-    <row r="19">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>350</v>
       </c>
@@ -7235,7 +6910,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -7246,7 +6921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>117</v>
       </c>
@@ -7257,7 +6932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>118</v>
       </c>
@@ -7268,7 +6943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>107</v>
       </c>
@@ -7279,7 +6954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>93</v>
       </c>
@@ -7290,7 +6965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>79</v>
       </c>
@@ -7301,7 +6976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>89</v>
       </c>
@@ -7312,7 +6987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>74</v>
       </c>
@@ -7323,7 +6998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>78</v>
       </c>
@@ -7334,7 +7009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>87</v>
       </c>
@@ -7345,7 +7020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -7356,7 +7031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>184</v>
       </c>
@@ -7367,7 +7042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>80</v>
       </c>
@@ -7378,7 +7053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>207</v>
       </c>
@@ -7389,7 +7064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>86</v>
       </c>
@@ -7400,7 +7075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>224</v>
       </c>
@@ -7411,7 +7086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>69</v>
       </c>
@@ -7422,7 +7097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>77</v>
       </c>
@@ -7433,7 +7108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -7444,7 +7119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>75</v>
       </c>
@@ -7455,7 +7130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -7466,7 +7141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>88</v>
       </c>
@@ -7477,7 +7152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>122</v>
       </c>
@@ -7488,7 +7163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>76</v>
       </c>
@@ -7499,7 +7174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -7510,7 +7185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>123</v>
       </c>
@@ -7521,7 +7196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -7532,7 +7207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>144</v>
       </c>
@@ -7543,7 +7218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>90</v>
       </c>
@@ -7554,7 +7229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>139</v>
       </c>
@@ -7565,7 +7240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>181</v>
       </c>
@@ -7575,10 +7250,8 @@
       <c r="C50" t="b">
         <v>1</v>
       </c>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-    </row>
-    <row r="51">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>202</v>
       </c>
@@ -7588,10 +7261,8 @@
       <c r="C51" t="b">
         <v>1</v>
       </c>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14"/>
-    </row>
-    <row r="52">
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>218</v>
       </c>
@@ -7602,7 +7273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>142</v>
       </c>
@@ -7613,7 +7284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -7624,7 +7295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>66</v>
       </c>
@@ -7635,7 +7306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -7646,7 +7317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>52</v>
       </c>
@@ -7657,43 +7328,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>309</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" t="s">
         <v>46</v>
       </c>
-      <c r="C59" s="18" t="b">
+      <c r="C59" t="b">
         <v>1</v>
       </c>
       <c r="D59" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>310</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" t="s">
         <v>46</v>
       </c>
-      <c r="C60" s="18" t="b">
+      <c r="C60" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>308</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" t="s">
         <v>46</v>
       </c>
-      <c r="C61" s="18" t="b">
+      <c r="C61" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>285</v>
       </c>
@@ -7704,7 +7375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>111</v>
       </c>
@@ -7715,7 +7386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>283</v>
       </c>
@@ -7726,40 +7397,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>295</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" t="s">
         <v>46</v>
       </c>
       <c r="C65" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="66" s="14" customFormat="1">
-      <c r="A66" s="4" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>296</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" t="s">
         <v>46</v>
       </c>
       <c r="C66" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="67" s="14" customFormat="1">
-      <c r="A67" s="4" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>294</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" t="s">
         <v>41</v>
       </c>
-      <c r="C67" s="18" t="b">
+      <c r="C67" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="68" s="14" customFormat="1">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>286</v>
       </c>
@@ -7770,7 +7441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>340</v>
       </c>
@@ -7781,7 +7452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>287</v>
       </c>
@@ -7792,7 +7463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>288</v>
       </c>
@@ -7803,7 +7474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>367</v>
       </c>
@@ -7814,7 +7485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>368</v>
       </c>
@@ -7825,7 +7496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>369</v>
       </c>
@@ -7836,43 +7507,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="4" t="s">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>256</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" t="s">
         <v>46</v>
       </c>
-      <c r="C75" s="14" t="b">
+      <c r="C75" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="4" t="s">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>257</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" t="s">
         <v>46</v>
       </c>
-      <c r="C76" s="14" t="b">
+      <c r="C76" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="4" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>258</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" t="s">
         <v>46</v>
       </c>
-      <c r="C77" s="14" t="b">
+      <c r="C77" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A59:C77">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A59:C77">
     <sortCondition ref="A59"/>
   </sortState>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/app/config/tables/MADTRIAL_FU_PHONE/Forms/MADTRIAL_FU_PHONE/MADTRIAL_FU_PHONE.xlsx
+++ b/app/config/tables/MADTRIAL_FU_PHONE/Forms/MADTRIAL_FU_PHONE/MADTRIAL_FU_PHONE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MADtrials2\MADtrial\app\config\tables\MADTRIAL_FU_PHONE\Forms\MADTRIAL_FU_PHONE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afisker\Documents\tablet\MAD\ver6\MADtrial\app\config\tables\MADTRIAL_FU_PHONE\Forms\MADTRIAL_FU_PHONE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B6D433-15AB-4D90-A8D3-DC3640758797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F83A7C-F559-4520-B8A5-717AB13FDF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="412">
   <si>
     <t>setting_name</t>
   </si>
@@ -1290,6 +1290,9 @@
   </si>
   <si>
     <t>Sarampo2</t>
+  </si>
+  <si>
+    <t>Makci</t>
   </si>
 </sst>
 </file>
@@ -1735,7 +1738,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>20250725</v>
+        <v>20260731</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -5490,7 +5493,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E146"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.54296875" bestFit="1" customWidth="1"/>
@@ -5734,7 +5737,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -5748,7 +5751,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>57</v>
       </c>
@@ -5762,7 +5765,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>57</v>
       </c>
@@ -5776,7 +5779,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -5790,7 +5793,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -5807,7 +5810,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -5821,7 +5824,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -5835,7 +5838,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -5850,7 +5853,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>51</v>
       </c>
@@ -5865,57 +5868,67 @@
         <v>134</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="E26" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E27" t="s">
         <v>98</v>
       </c>
-      <c r="B27" t="str">
+      <c r="F27" t="str">
         <f>"2"</f>
         <v>2</v>
       </c>
-      <c r="C27" t="s">
+      <c r="G27" t="s">
         <v>400</v>
       </c>
-      <c r="D27" t="s">
+      <c r="H27" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E28" t="s">
         <v>98</v>
       </c>
-      <c r="B28" t="str">
+      <c r="F28" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
-      <c r="C28" t="s">
+      <c r="G28" t="s">
         <v>398</v>
       </c>
-      <c r="D28" t="s">
+      <c r="H28" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>98</v>
       </c>
       <c r="B29" t="str">
+        <f>"14"</f>
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>411</v>
+      </c>
+      <c r="D29" t="s">
+        <v>411</v>
+      </c>
+      <c r="E29" t="str">
         <f>"10"</f>
         <v>10</v>
       </c>
-      <c r="C29" t="s">
+      <c r="F29" t="s">
         <v>397</v>
       </c>
-      <c r="D29" t="s">
+      <c r="G29" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>98</v>
       </c>
@@ -5933,7 +5946,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>98</v>
       </c>
@@ -5948,7 +5961,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>98</v>
       </c>
